--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 бррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 бррсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\04,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3227C7-AFDB-4121-8F18-C5C89BC9FB1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934D7090-BA5F-44F3-810C-08950E52B82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$131</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -735,7 +727,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -755,10 +747,8 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1074,12 +1064,13 @@
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="22" width="7" customWidth="1"/>
-    <col min="23" max="23" width="7" style="22" customWidth="1"/>
+    <col min="23" max="23" width="7" style="20" customWidth="1"/>
     <col min="24" max="25" width="5" customWidth="1"/>
     <col min="26" max="35" width="6" customWidth="1"/>
     <col min="36" max="36" width="26.42578125" customWidth="1"/>
     <col min="37" max="37" width="7" customWidth="1"/>
-    <col min="38" max="48" width="3" customWidth="1"/>
+    <col min="38" max="38" width="5.85546875" customWidth="1"/>
+    <col min="39" max="48" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -1584,7 +1575,7 @@
         <f>U6</f>
         <v>0</v>
       </c>
-      <c r="W6" s="19"/>
+      <c r="W6" s="9"/>
       <c r="X6" s="9">
         <f>(F6+O6+P6+Q6+R6+S6+V6)/T6</f>
         <v>20.761651319828115</v>
@@ -1628,7 +1619,10 @@
         <f>ROUND(G6*V6,0)</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="9"/>
+      <c r="AL6" s="9">
+        <f>(SUM(Z6:AI6)+T6)/11</f>
+        <v>49.530909090909084</v>
+      </c>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
       <c r="AO6" s="9"/>
@@ -1689,7 +1683,7 @@
         <f t="shared" ref="V7:V70" si="6">U7</f>
         <v>0</v>
       </c>
-      <c r="W7" s="20"/>
+      <c r="W7" s="11"/>
       <c r="X7" s="9" t="e">
         <f t="shared" ref="X7:X70" si="7">(F7+O7+P7+Q7+R7+S7+V7)/T7</f>
         <v>#DIV/0!</v>
@@ -1733,7 +1727,10 @@
         <f t="shared" ref="AK7:AK70" si="8">ROUND(G7*V7,0)</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="9"/>
+      <c r="AL7" s="9">
+        <f t="shared" ref="AL7:AL70" si="9">(SUM(Z7:AI7)+T7)/11</f>
+        <v>0</v>
+      </c>
       <c r="AM7" s="9"/>
       <c r="AN7" s="9"/>
       <c r="AO7" s="9"/>
@@ -1800,14 +1797,14 @@
         <v>63.0702</v>
       </c>
       <c r="U8" s="4">
-        <f t="shared" ref="U8:U9" si="9">11*T8-S8-R8-Q8-P8-O8-F8</f>
+        <f t="shared" ref="U8:U9" si="10">11*T8-S8-R8-Q8-P8-O8-F8</f>
         <v>78.190200000000004</v>
       </c>
       <c r="V8" s="4">
         <f t="shared" si="6"/>
         <v>78.190200000000004</v>
       </c>
-      <c r="W8" s="19"/>
+      <c r="W8" s="9"/>
       <c r="X8" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -1851,7 +1848,10 @@
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="AL8" s="9"/>
+      <c r="AL8" s="9">
+        <f t="shared" si="9"/>
+        <v>57.986872727272726</v>
+      </c>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
       <c r="AO8" s="9"/>
@@ -1920,14 +1920,14 @@
         <v>73.171999999999997</v>
       </c>
       <c r="U9" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>59.634999999999934</v>
       </c>
       <c r="V9" s="4">
         <f t="shared" si="6"/>
         <v>59.634999999999934</v>
       </c>
-      <c r="W9" s="19"/>
+      <c r="W9" s="9"/>
       <c r="X9" s="9">
         <f t="shared" si="7"/>
         <v>11.000000000000002</v>
@@ -1971,7 +1971,10 @@
         <f t="shared" si="8"/>
         <v>60</v>
       </c>
-      <c r="AL9" s="9"/>
+      <c r="AL9" s="9">
+        <f t="shared" si="9"/>
+        <v>64.518600000000006</v>
+      </c>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="9"/>
@@ -2030,7 +2033,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W10" s="20"/>
+      <c r="W10" s="11"/>
       <c r="X10" s="9" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -2076,7 +2079,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL10" s="9"/>
+      <c r="AL10" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
       <c r="AO10" s="9"/>
@@ -2147,7 +2153,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W11" s="19"/>
+      <c r="W11" s="9"/>
       <c r="X11" s="9">
         <f t="shared" si="7"/>
         <v>14.877019438444925</v>
@@ -2191,7 +2197,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="9"/>
+      <c r="AL11" s="9">
+        <f t="shared" si="9"/>
+        <v>108.78181818181817</v>
+      </c>
       <c r="AM11" s="9"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="9"/>
@@ -2262,7 +2271,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W12" s="19"/>
+      <c r="W12" s="9"/>
       <c r="X12" s="9">
         <f t="shared" si="7"/>
         <v>12.39882697947214</v>
@@ -2306,7 +2315,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="9"/>
+      <c r="AL12" s="9">
+        <f t="shared" si="9"/>
+        <v>127.87272727272729</v>
+      </c>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
       <c r="AO12" s="9"/>
@@ -2377,7 +2389,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W13" s="19"/>
+      <c r="W13" s="9"/>
       <c r="X13" s="9">
         <f t="shared" si="7"/>
         <v>11.133333333333333</v>
@@ -2421,7 +2433,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="9"/>
+      <c r="AL13" s="9">
+        <f t="shared" si="9"/>
+        <v>17.327272727272728</v>
+      </c>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
       <c r="AO13" s="9"/>
@@ -2492,7 +2507,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W14" s="19"/>
+      <c r="W14" s="9"/>
       <c r="X14" s="9">
         <f t="shared" si="7"/>
         <v>11.828282828282831</v>
@@ -2536,7 +2551,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="9"/>
+      <c r="AL14" s="9">
+        <f t="shared" si="9"/>
+        <v>22.436363636363634</v>
+      </c>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
       <c r="AO14" s="9"/>
@@ -2607,7 +2625,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W15" s="19"/>
+      <c r="W15" s="9"/>
       <c r="X15" s="9">
         <f t="shared" si="7"/>
         <v>13.76923076923077</v>
@@ -2651,7 +2669,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="9"/>
+      <c r="AL15" s="9">
+        <f t="shared" si="9"/>
+        <v>25.290909090909089</v>
+      </c>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
       <c r="AO15" s="9"/>
@@ -2722,7 +2743,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W16" s="19"/>
+      <c r="W16" s="9"/>
       <c r="X16" s="9">
         <f t="shared" si="7"/>
         <v>15.379901480328057</v>
@@ -2766,7 +2787,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="9"/>
+      <c r="AL16" s="9">
+        <f t="shared" si="9"/>
+        <v>98.264327272727272</v>
+      </c>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
       <c r="AO16" s="9"/>
@@ -2839,7 +2863,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W17" s="19"/>
+      <c r="W17" s="9"/>
       <c r="X17" s="9">
         <f t="shared" si="7"/>
         <v>17.54240202655097</v>
@@ -2883,7 +2907,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="9"/>
+      <c r="AL17" s="9">
+        <f t="shared" si="9"/>
+        <v>438.83512727272733</v>
+      </c>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
       <c r="AO17" s="9"/>
@@ -2952,7 +2979,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W18" s="19"/>
+      <c r="W18" s="9"/>
       <c r="X18" s="9">
         <f t="shared" si="7"/>
         <v>20.939735518587554</v>
@@ -2996,7 +3023,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="9"/>
+      <c r="AL18" s="9">
+        <f t="shared" si="9"/>
+        <v>14.592509090909088</v>
+      </c>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
       <c r="AO18" s="9"/>
@@ -3067,7 +3097,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W19" s="19"/>
+      <c r="W19" s="9"/>
       <c r="X19" s="9">
         <f t="shared" si="7"/>
         <v>13.380020122411338</v>
@@ -3111,7 +3141,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="9"/>
+      <c r="AL19" s="9">
+        <f t="shared" si="9"/>
+        <v>6.6403454545454537</v>
+      </c>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
       <c r="AO19" s="9"/>
@@ -3182,7 +3215,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W20" s="19"/>
+      <c r="W20" s="9"/>
       <c r="X20" s="9">
         <f t="shared" si="7"/>
         <v>20.396756860487429</v>
@@ -3228,7 +3261,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="9"/>
+      <c r="AL20" s="9">
+        <f t="shared" si="9"/>
+        <v>3.2633818181818186</v>
+      </c>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
       <c r="AO20" s="9"/>
@@ -3301,7 +3337,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W21" s="19"/>
+      <c r="W21" s="9"/>
       <c r="X21" s="9">
         <f t="shared" si="7"/>
         <v>13.710179252235188</v>
@@ -3345,7 +3381,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="9"/>
+      <c r="AL21" s="9">
+        <f t="shared" si="9"/>
+        <v>82.219345454545461</v>
+      </c>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
       <c r="AO21" s="9"/>
@@ -3416,7 +3455,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W22" s="19"/>
+      <c r="W22" s="9"/>
       <c r="X22" s="9">
         <f t="shared" si="7"/>
         <v>15.475915092314295</v>
@@ -3460,7 +3499,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="9"/>
+      <c r="AL22" s="9">
+        <f t="shared" si="9"/>
+        <v>21.99281818181818</v>
+      </c>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
       <c r="AO22" s="9"/>
@@ -3531,7 +3573,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W23" s="19"/>
+      <c r="W23" s="9"/>
       <c r="X23" s="9">
         <f t="shared" si="7"/>
         <v>14.599536452715881</v>
@@ -3575,7 +3617,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="9"/>
+      <c r="AL23" s="9">
+        <f t="shared" si="9"/>
+        <v>38.019309090909097</v>
+      </c>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
       <c r="AO23" s="9"/>
@@ -3646,7 +3691,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W24" s="19"/>
+      <c r="W24" s="9"/>
       <c r="X24" s="9">
         <f t="shared" si="7"/>
         <v>28.255033557046978</v>
@@ -3690,7 +3735,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="9"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="9"/>
+        <v>4.0744545454545449</v>
+      </c>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
       <c r="AO24" s="9"/>
@@ -3761,7 +3809,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W25" s="19"/>
+      <c r="W25" s="9"/>
       <c r="X25" s="9">
         <f t="shared" si="7"/>
         <v>14.849150820807015</v>
@@ -3805,7 +3853,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="9"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="9"/>
+        <v>44.2376</v>
+      </c>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
       <c r="AO25" s="9"/>
@@ -3864,7 +3915,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W26" s="20"/>
+      <c r="W26" s="11"/>
       <c r="X26" s="9" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -3910,7 +3961,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL26" s="9"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
       <c r="AO26" s="9"/>
@@ -3980,7 +4034,7 @@
         <f t="shared" si="6"/>
         <v>151.69779999999997</v>
       </c>
-      <c r="W27" s="19"/>
+      <c r="W27" s="9"/>
       <c r="X27" s="9">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -4026,7 +4080,10 @@
         <f t="shared" si="8"/>
         <v>152</v>
       </c>
-      <c r="AL27" s="9"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="9"/>
+        <v>2.6847272727272724</v>
+      </c>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
       <c r="AO27" s="9"/>
@@ -4099,7 +4156,7 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="W28" s="21"/>
+      <c r="W28" s="19"/>
       <c r="X28" s="9">
         <f t="shared" si="7"/>
         <v>2.060761871408332</v>
@@ -4143,7 +4200,10 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AL28" s="9"/>
+      <c r="AL28" s="9">
+        <f t="shared" si="9"/>
+        <v>34.961581818181806</v>
+      </c>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
       <c r="AO28" s="9"/>
@@ -4214,7 +4274,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W29" s="19"/>
+      <c r="W29" s="9"/>
       <c r="X29" s="9">
         <f t="shared" si="7"/>
         <v>110.75720847860977</v>
@@ -4258,7 +4318,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="9"/>
+      <c r="AL29" s="9">
+        <f t="shared" si="9"/>
+        <v>39.956745454545455</v>
+      </c>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9"/>
@@ -4335,7 +4398,7 @@
         <f t="shared" si="6"/>
         <v>400</v>
       </c>
-      <c r="W30" s="21"/>
+      <c r="W30" s="19"/>
       <c r="X30" s="9">
         <f t="shared" si="7"/>
         <v>7.3995569439135824</v>
@@ -4379,7 +4442,10 @@
         <f t="shared" si="8"/>
         <v>400</v>
       </c>
-      <c r="AL30" s="9"/>
+      <c r="AL30" s="9">
+        <f t="shared" si="9"/>
+        <v>175.87180000000001</v>
+      </c>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9"/>
@@ -4446,7 +4512,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W31" s="19"/>
+      <c r="W31" s="9"/>
       <c r="X31" s="9" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -4490,7 +4556,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="9"/>
+      <c r="AL31" s="9">
+        <f t="shared" si="9"/>
+        <v>0.84945454545454524</v>
+      </c>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9"/>
@@ -4561,7 +4630,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W32" s="19"/>
+      <c r="W32" s="9"/>
       <c r="X32" s="9">
         <f t="shared" si="7"/>
         <v>32.873137589892323</v>
@@ -4605,7 +4674,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="9"/>
+      <c r="AL32" s="9">
+        <f t="shared" si="9"/>
+        <v>14.363072727272732</v>
+      </c>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
       <c r="AO32" s="9"/>
@@ -4676,7 +4748,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W33" s="19"/>
+      <c r="W33" s="9"/>
       <c r="X33" s="9">
         <f t="shared" si="7"/>
         <v>11.681976016473532</v>
@@ -4720,7 +4792,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="9"/>
+      <c r="AL33" s="9">
+        <f t="shared" si="9"/>
+        <v>19.827963636363645</v>
+      </c>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
       <c r="AO33" s="9"/>
@@ -4785,14 +4860,14 @@
         <v>14.658600000000002</v>
       </c>
       <c r="U34" s="4">
-        <f t="shared" ref="U34:U42" si="10">11*T34-S34-R34-Q34-P34-O34-F34</f>
+        <f t="shared" ref="U34:U42" si="11">11*T34-S34-R34-Q34-P34-O34-F34</f>
         <v>33.194600000000008</v>
       </c>
       <c r="V34" s="4">
         <f t="shared" si="6"/>
         <v>33.194600000000008</v>
       </c>
-      <c r="W34" s="19"/>
+      <c r="W34" s="9"/>
       <c r="X34" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -4836,7 +4911,10 @@
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
-      <c r="AL34" s="9"/>
+      <c r="AL34" s="9">
+        <f t="shared" si="9"/>
+        <v>13.305909090909092</v>
+      </c>
       <c r="AM34" s="9"/>
       <c r="AN34" s="9"/>
       <c r="AO34" s="9"/>
@@ -4905,14 +4983,14 @@
         <v>278.8</v>
       </c>
       <c r="U35" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>223.80000000000018</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" si="6"/>
         <v>223.80000000000018</v>
       </c>
-      <c r="W35" s="19"/>
+      <c r="W35" s="9"/>
       <c r="X35" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -4956,7 +5034,10 @@
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
-      <c r="AL35" s="9"/>
+      <c r="AL35" s="9">
+        <f t="shared" si="9"/>
+        <v>327.61872727272726</v>
+      </c>
       <c r="AM35" s="9"/>
       <c r="AN35" s="9"/>
       <c r="AO35" s="9"/>
@@ -5027,7 +5108,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W36" s="19"/>
+      <c r="W36" s="9"/>
       <c r="X36" s="9">
         <f t="shared" si="7"/>
         <v>15.443808139534879</v>
@@ -5071,7 +5152,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="9"/>
+      <c r="AL36" s="9">
+        <f t="shared" si="9"/>
+        <v>69.218181818181819</v>
+      </c>
       <c r="AM36" s="9"/>
       <c r="AN36" s="9"/>
       <c r="AO36" s="9"/>
@@ -5144,7 +5228,7 @@
         <f t="shared" si="6"/>
         <v>200</v>
       </c>
-      <c r="W37" s="21"/>
+      <c r="W37" s="19"/>
       <c r="X37" s="9">
         <f t="shared" si="7"/>
         <v>9.6660117878192544</v>
@@ -5188,7 +5272,10 @@
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="AL37" s="9"/>
+      <c r="AL37" s="9">
+        <f t="shared" si="9"/>
+        <v>126.1090909090909</v>
+      </c>
       <c r="AM37" s="9"/>
       <c r="AN37" s="9"/>
       <c r="AO37" s="9"/>
@@ -5233,11 +5320,11 @@
         <v>104</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>-1</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:M69" si="12">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="13">E38-N38</f>
         <v>103</v>
       </c>
       <c r="N38" s="9"/>
@@ -5251,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="9">
-        <f t="shared" ref="T38:T69" si="13">M38/5</f>
+        <f t="shared" ref="T38:T69" si="14">M38/5</f>
         <v>20.6</v>
       </c>
       <c r="U38" s="4"/>
@@ -5259,13 +5346,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W38" s="19"/>
+      <c r="W38" s="9"/>
       <c r="X38" s="9">
         <f t="shared" si="7"/>
         <v>10.796116504854368</v>
       </c>
       <c r="Y38" s="9">
-        <f t="shared" ref="Y38:Y69" si="14">(F38+O38+P38+Q38+R38+S38)/T38</f>
+        <f t="shared" ref="Y38:Y69" si="15">(F38+O38+P38+Q38+R38+S38)/T38</f>
         <v>10.796116504854368</v>
       </c>
       <c r="Z38" s="9">
@@ -5303,7 +5390,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL38" s="9"/>
+      <c r="AL38" s="9">
+        <f t="shared" si="9"/>
+        <v>19.654545454545456</v>
+      </c>
       <c r="AM38" s="9"/>
       <c r="AN38" s="9"/>
       <c r="AO38" s="9"/>
@@ -5348,11 +5438,11 @@
         <v>32.700000000000003</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.5250000000000021</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.175000000000001</v>
       </c>
       <c r="N39" s="9"/>
@@ -5366,24 +5456,24 @@
         <v>0</v>
       </c>
       <c r="T39" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.0350000000000001</v>
       </c>
       <c r="U39" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31.424000000000007</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" si="6"/>
         <v>31.424000000000007</v>
       </c>
-      <c r="W39" s="19"/>
+      <c r="W39" s="9"/>
       <c r="X39" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="Y39" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.7930405965202976</v>
       </c>
       <c r="Z39" s="9">
@@ -5423,7 +5513,10 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="AL39" s="9"/>
+      <c r="AL39" s="9">
+        <f t="shared" si="9"/>
+        <v>4.0202909090909094</v>
+      </c>
       <c r="AM39" s="9"/>
       <c r="AN39" s="9"/>
       <c r="AO39" s="9"/>
@@ -5469,11 +5562,11 @@
         <v>106</v>
       </c>
       <c r="L40" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5</v>
       </c>
       <c r="M40" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>101</v>
       </c>
       <c r="N40" s="9"/>
@@ -5487,7 +5580,7 @@
         <v>103.60000000000009</v>
       </c>
       <c r="T40" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.2</v>
       </c>
       <c r="U40" s="4"/>
@@ -5495,13 +5588,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W40" s="19"/>
+      <c r="W40" s="9"/>
       <c r="X40" s="9">
         <f t="shared" si="7"/>
         <v>11.46534653465347</v>
       </c>
       <c r="Y40" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.46534653465347</v>
       </c>
       <c r="Z40" s="9">
@@ -5539,7 +5632,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="9"/>
+      <c r="AL40" s="9">
+        <f t="shared" si="9"/>
+        <v>17.054545454545455</v>
+      </c>
       <c r="AM40" s="9"/>
       <c r="AN40" s="9"/>
       <c r="AO40" s="9"/>
@@ -5584,11 +5680,11 @@
         <v>91</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-12</v>
       </c>
       <c r="M41" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>79</v>
       </c>
       <c r="N41" s="9"/>
@@ -5602,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.8</v>
       </c>
       <c r="U41" s="4">
@@ -5613,13 +5709,13 @@
         <f t="shared" si="6"/>
         <v>72</v>
       </c>
-      <c r="W41" s="19"/>
+      <c r="W41" s="9"/>
       <c r="X41" s="9">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Y41" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.44303797468354428</v>
       </c>
       <c r="Z41" s="9">
@@ -5657,7 +5753,10 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="AL41" s="9"/>
+      <c r="AL41" s="9">
+        <f t="shared" si="9"/>
+        <v>18.963636363636365</v>
+      </c>
       <c r="AM41" s="9"/>
       <c r="AN41" s="9"/>
       <c r="AO41" s="9"/>
@@ -5700,11 +5799,11 @@
         <v>66.900000000000006</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.3020000000000067</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>64.597999999999999</v>
       </c>
       <c r="N42" s="9"/>
@@ -5718,24 +5817,24 @@
         <v>89.7376</v>
       </c>
       <c r="T42" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.919599999999999</v>
       </c>
       <c r="U42" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>30.612000000000002</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="6"/>
         <v>30.612000000000002</v>
       </c>
-      <c r="W42" s="19"/>
+      <c r="W42" s="9"/>
       <c r="X42" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="Y42" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.6305767980432844</v>
       </c>
       <c r="Z42" s="9">
@@ -5773,7 +5872,10 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="AL42" s="9"/>
+      <c r="AL42" s="9">
+        <f t="shared" si="9"/>
+        <v>6.405636363636364</v>
+      </c>
       <c r="AM42" s="9"/>
       <c r="AN42" s="9"/>
       <c r="AO42" s="9"/>
@@ -5816,11 +5918,11 @@
         <v>16</v>
       </c>
       <c r="L43" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M43" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="N43" s="11"/>
@@ -5832,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.2</v>
       </c>
       <c r="U43" s="13"/>
@@ -5840,13 +5942,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W43" s="20"/>
+      <c r="W43" s="11"/>
       <c r="X43" s="9">
         <f t="shared" si="7"/>
         <v>11.5625</v>
       </c>
       <c r="Y43" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.5625</v>
       </c>
       <c r="Z43" s="11">
@@ -5884,7 +5986,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL43" s="9"/>
+      <c r="AL43" s="9">
+        <f t="shared" si="9"/>
+        <v>7.0909090909090908</v>
+      </c>
       <c r="AM43" s="9"/>
       <c r="AN43" s="9"/>
       <c r="AO43" s="9"/>
@@ -5929,11 +6034,11 @@
         <v>191</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-206</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-15</v>
       </c>
       <c r="N44" s="9"/>
@@ -5947,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-3</v>
       </c>
       <c r="U44" s="4"/>
@@ -5955,13 +6060,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W44" s="19"/>
+      <c r="W44" s="9"/>
       <c r="X44" s="9">
         <f t="shared" si="7"/>
         <v>-2</v>
       </c>
       <c r="Y44" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="Z44" s="9">
@@ -5999,7 +6104,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL44" s="9"/>
+      <c r="AL44" s="9">
+        <f t="shared" si="9"/>
+        <v>24.254545454545454</v>
+      </c>
       <c r="AM44" s="9"/>
       <c r="AN44" s="9"/>
       <c r="AO44" s="9"/>
@@ -6044,11 +6152,11 @@
         <v>152</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-147</v>
       </c>
       <c r="M45" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="N45" s="9"/>
@@ -6062,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="U45" s="4"/>
@@ -6070,13 +6178,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W45" s="19"/>
+      <c r="W45" s="9"/>
       <c r="X45" s="9">
         <f t="shared" si="7"/>
         <v>396</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>396</v>
       </c>
       <c r="Z45" s="9">
@@ -6114,7 +6222,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL45" s="9"/>
+      <c r="AL45" s="9">
+        <f t="shared" si="9"/>
+        <v>31.290909090909089</v>
+      </c>
       <c r="AM45" s="9"/>
       <c r="AN45" s="9"/>
       <c r="AO45" s="9"/>
@@ -6159,11 +6270,11 @@
         <v>104</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.1809999999999974</v>
       </c>
       <c r="M46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100.819</v>
       </c>
       <c r="N46" s="9"/>
@@ -6177,24 +6288,24 @@
         <v>101.8304</v>
       </c>
       <c r="T46" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.163800000000002</v>
       </c>
       <c r="U46" s="4">
-        <f t="shared" ref="U46:U62" si="15">11*T46-S46-R46-Q46-P46-O46-F46</f>
+        <f t="shared" ref="U46:U62" si="16">11*T46-S46-R46-Q46-P46-O46-F46</f>
         <v>4.481400000000022</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="6"/>
         <v>4.481400000000022</v>
       </c>
-      <c r="W46" s="19"/>
+      <c r="W46" s="9"/>
       <c r="X46" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.777750225651911</v>
       </c>
       <c r="Z46" s="9">
@@ -6232,7 +6343,10 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AL46" s="9"/>
+      <c r="AL46" s="9">
+        <f t="shared" si="9"/>
+        <v>19.562927272727276</v>
+      </c>
       <c r="AM46" s="9"/>
       <c r="AN46" s="9"/>
       <c r="AO46" s="9"/>
@@ -6277,11 +6391,11 @@
         <v>215</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-29</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>186</v>
       </c>
       <c r="N47" s="9"/>
@@ -6297,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>37.200000000000003</v>
       </c>
       <c r="U47" s="4"/>
@@ -6305,13 +6419,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W47" s="19"/>
+      <c r="W47" s="9"/>
       <c r="X47" s="9">
         <f t="shared" si="7"/>
         <v>21.370967741935484</v>
       </c>
       <c r="Y47" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>21.370967741935484</v>
       </c>
       <c r="Z47" s="9">
@@ -6349,7 +6463,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL47" s="9"/>
+      <c r="AL47" s="9">
+        <f t="shared" si="9"/>
+        <v>47.781818181818181</v>
+      </c>
       <c r="AM47" s="9"/>
       <c r="AN47" s="9"/>
       <c r="AO47" s="9"/>
@@ -6394,11 +6511,11 @@
         <v>373</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-169</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>204</v>
       </c>
       <c r="N48" s="9"/>
@@ -6414,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>40.799999999999997</v>
       </c>
       <c r="U48" s="4"/>
@@ -6422,13 +6539,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W48" s="19"/>
+      <c r="W48" s="9"/>
       <c r="X48" s="9">
         <f t="shared" si="7"/>
         <v>11.029411764705882</v>
       </c>
       <c r="Y48" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.029411764705882</v>
       </c>
       <c r="Z48" s="9">
@@ -6466,7 +6583,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL48" s="9"/>
+      <c r="AL48" s="9">
+        <f t="shared" si="9"/>
+        <v>51.891418181818175</v>
+      </c>
       <c r="AM48" s="9"/>
       <c r="AN48" s="9"/>
       <c r="AO48" s="9"/>
@@ -6511,11 +6631,11 @@
         <v>71.8</v>
       </c>
       <c r="L49" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.8430000000000035</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>69.956999999999994</v>
       </c>
       <c r="N49" s="9"/>
@@ -6529,7 +6649,7 @@
         <v>92.494599999999977</v>
       </c>
       <c r="T49" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.991399999999999</v>
       </c>
       <c r="U49" s="4"/>
@@ -6537,13 +6657,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W49" s="19"/>
+      <c r="W49" s="9"/>
       <c r="X49" s="9">
         <f t="shared" si="7"/>
         <v>13.979616049859199</v>
       </c>
       <c r="Y49" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.979616049859199</v>
       </c>
       <c r="Z49" s="9">
@@ -6581,7 +6701,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL49" s="9"/>
+      <c r="AL49" s="9">
+        <f t="shared" si="9"/>
+        <v>16.196527272727273</v>
+      </c>
       <c r="AM49" s="9"/>
       <c r="AN49" s="9"/>
       <c r="AO49" s="9"/>
@@ -6626,11 +6749,11 @@
         <v>127.38</v>
       </c>
       <c r="L50" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-17.199999999999989</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>110.18</v>
       </c>
       <c r="N50" s="9"/>
@@ -6644,7 +6767,7 @@
         <v>39.322400000000073</v>
       </c>
       <c r="T50" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.036000000000001</v>
       </c>
       <c r="U50" s="4"/>
@@ -6652,13 +6775,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W50" s="19"/>
+      <c r="W50" s="9"/>
       <c r="X50" s="9">
         <f t="shared" si="7"/>
         <v>13.157760029043386</v>
       </c>
       <c r="Y50" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.157760029043386</v>
       </c>
       <c r="Z50" s="9">
@@ -6696,7 +6819,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL50" s="9"/>
+      <c r="AL50" s="9">
+        <f t="shared" si="9"/>
+        <v>28.08616363636364</v>
+      </c>
       <c r="AM50" s="9"/>
       <c r="AN50" s="9"/>
       <c r="AO50" s="9"/>
@@ -6741,11 +6867,11 @@
         <v>14.4</v>
       </c>
       <c r="L51" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.0060000000000002</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.3940000000000001</v>
       </c>
       <c r="N51" s="9"/>
@@ -6759,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.4788000000000001</v>
       </c>
       <c r="U51" s="4"/>
@@ -6767,13 +6893,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W51" s="19"/>
+      <c r="W51" s="9"/>
       <c r="X51" s="9">
         <f t="shared" si="7"/>
         <v>157.30998106572895</v>
       </c>
       <c r="Y51" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>157.30998106572895</v>
       </c>
       <c r="Z51" s="9">
@@ -6811,7 +6937,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL51" s="9"/>
+      <c r="AL51" s="9">
+        <f t="shared" si="9"/>
+        <v>22.699436363636366</v>
+      </c>
       <c r="AM51" s="9"/>
       <c r="AN51" s="9"/>
       <c r="AO51" s="9"/>
@@ -6856,11 +6985,11 @@
         <v>155</v>
       </c>
       <c r="L52" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>148</v>
       </c>
       <c r="N52" s="9"/>
@@ -6874,7 +7003,7 @@
         <v>246.8</v>
       </c>
       <c r="T52" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>29.6</v>
       </c>
       <c r="U52" s="4"/>
@@ -6882,13 +7011,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W52" s="19"/>
+      <c r="W52" s="9"/>
       <c r="X52" s="9">
         <f t="shared" si="7"/>
         <v>14.554054054054054</v>
       </c>
       <c r="Y52" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.554054054054054</v>
       </c>
       <c r="Z52" s="9">
@@ -6926,7 +7055,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL52" s="9"/>
+      <c r="AL52" s="9">
+        <f t="shared" si="9"/>
+        <v>31.763636363636365</v>
+      </c>
       <c r="AM52" s="9"/>
       <c r="AN52" s="9"/>
       <c r="AO52" s="9"/>
@@ -6971,11 +7103,11 @@
         <v>219</v>
       </c>
       <c r="L53" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>213</v>
       </c>
       <c r="N53" s="9"/>
@@ -6989,7 +7121,7 @@
         <v>368.39600000000007</v>
       </c>
       <c r="T53" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42.6</v>
       </c>
       <c r="U53" s="4"/>
@@ -6997,13 +7129,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W53" s="19"/>
+      <c r="W53" s="9"/>
       <c r="X53" s="9">
         <f t="shared" si="7"/>
         <v>16.680657276995305</v>
       </c>
       <c r="Y53" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.680657276995305</v>
       </c>
       <c r="Z53" s="9">
@@ -7041,7 +7173,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL53" s="9"/>
+      <c r="AL53" s="9">
+        <f t="shared" si="9"/>
+        <v>53.000000000000007</v>
+      </c>
       <c r="AM53" s="9"/>
       <c r="AN53" s="9"/>
       <c r="AO53" s="9"/>
@@ -7086,11 +7221,11 @@
         <v>38</v>
       </c>
       <c r="L54" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-13</v>
       </c>
       <c r="M54" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>25</v>
       </c>
       <c r="N54" s="9"/>
@@ -7104,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="U54" s="4"/>
@@ -7112,13 +7247,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W54" s="19"/>
+      <c r="W54" s="9"/>
       <c r="X54" s="9">
         <f t="shared" si="7"/>
         <v>11.6</v>
       </c>
       <c r="Y54" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.6</v>
       </c>
       <c r="Z54" s="9">
@@ -7156,7 +7291,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL54" s="9"/>
+      <c r="AL54" s="9">
+        <f t="shared" si="9"/>
+        <v>4.254545454545454</v>
+      </c>
       <c r="AM54" s="9"/>
       <c r="AN54" s="9"/>
       <c r="AO54" s="9"/>
@@ -7201,11 +7339,11 @@
         <v>45</v>
       </c>
       <c r="L55" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9</v>
       </c>
       <c r="M55" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="N55" s="9"/>
@@ -7219,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.2</v>
       </c>
       <c r="U55" s="17">
@@ -7229,13 +7367,13 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="W55" s="21"/>
+      <c r="W55" s="19"/>
       <c r="X55" s="9">
         <f t="shared" si="7"/>
         <v>5.416666666666667</v>
       </c>
       <c r="Y55" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.25</v>
       </c>
       <c r="Z55" s="9">
@@ -7273,7 +7411,10 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AL55" s="9"/>
+      <c r="AL55" s="9">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
       <c r="AM55" s="9"/>
       <c r="AN55" s="9"/>
       <c r="AO55" s="9"/>
@@ -7318,11 +7459,11 @@
         <v>37.5</v>
       </c>
       <c r="L56" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.6929999999999978</v>
       </c>
       <c r="M56" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34.807000000000002</v>
       </c>
       <c r="N56" s="9"/>
@@ -7336,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.9614000000000003</v>
       </c>
       <c r="U56" s="4"/>
@@ -7344,13 +7485,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W56" s="19"/>
+      <c r="W56" s="9"/>
       <c r="X56" s="9">
         <f t="shared" si="7"/>
         <v>22.764271554572357</v>
       </c>
       <c r="Y56" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22.764271554572357</v>
       </c>
       <c r="Z56" s="9">
@@ -7388,7 +7529,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL56" s="9"/>
+      <c r="AL56" s="9">
+        <f t="shared" si="9"/>
+        <v>12.522399999999999</v>
+      </c>
       <c r="AM56" s="9"/>
       <c r="AN56" s="9"/>
       <c r="AO56" s="9"/>
@@ -7433,11 +7577,11 @@
         <v>99</v>
       </c>
       <c r="L57" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5</v>
       </c>
       <c r="M57" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>94</v>
       </c>
       <c r="N57" s="9"/>
@@ -7451,24 +7595,24 @@
         <v>10.600000000000019</v>
       </c>
       <c r="T57" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18.8</v>
       </c>
       <c r="U57" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>82.199999999999989</v>
       </c>
       <c r="V57" s="4">
         <f t="shared" si="6"/>
         <v>82.199999999999989</v>
       </c>
-      <c r="W57" s="19"/>
+      <c r="W57" s="9"/>
       <c r="X57" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="Y57" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.627659574468086</v>
       </c>
       <c r="Z57" s="9">
@@ -7506,7 +7650,10 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="AL57" s="9"/>
+      <c r="AL57" s="9">
+        <f t="shared" si="9"/>
+        <v>12.254545454545456</v>
+      </c>
       <c r="AM57" s="9"/>
       <c r="AN57" s="9"/>
       <c r="AO57" s="9"/>
@@ -7551,11 +7698,11 @@
         <v>97.9</v>
       </c>
       <c r="L58" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-23.103999999999999</v>
       </c>
       <c r="M58" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>74.796000000000006</v>
       </c>
       <c r="N58" s="9"/>
@@ -7569,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.959200000000001</v>
       </c>
       <c r="U58" s="4"/>
@@ -7577,13 +7724,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W58" s="19"/>
+      <c r="W58" s="9"/>
       <c r="X58" s="9">
         <f t="shared" si="7"/>
         <v>19.681734317343171</v>
       </c>
       <c r="Y58" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>19.681734317343171</v>
       </c>
       <c r="Z58" s="9">
@@ -7621,7 +7768,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL58" s="9"/>
+      <c r="AL58" s="9">
+        <f t="shared" si="9"/>
+        <v>29.497436363636361</v>
+      </c>
       <c r="AM58" s="9"/>
       <c r="AN58" s="9"/>
       <c r="AO58" s="9"/>
@@ -7666,11 +7816,11 @@
         <v>23</v>
       </c>
       <c r="L59" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4800000000000004</v>
       </c>
       <c r="M59" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.48</v>
       </c>
       <c r="N59" s="9"/>
@@ -7684,7 +7834,7 @@
         <v>12.45080000000001</v>
       </c>
       <c r="T59" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8959999999999999</v>
       </c>
       <c r="U59" s="4"/>
@@ -7692,13 +7842,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W59" s="19"/>
+      <c r="W59" s="9"/>
       <c r="X59" s="9">
         <f t="shared" si="7"/>
         <v>11.397426470588236</v>
       </c>
       <c r="Y59" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.397426470588236</v>
       </c>
       <c r="Z59" s="9">
@@ -7736,7 +7886,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL59" s="9"/>
+      <c r="AL59" s="9">
+        <f t="shared" si="9"/>
+        <v>6.9241999999999999</v>
+      </c>
       <c r="AM59" s="9"/>
       <c r="AN59" s="9"/>
       <c r="AO59" s="9"/>
@@ -7781,11 +7934,11 @@
         <v>104</v>
       </c>
       <c r="L60" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-15</v>
       </c>
       <c r="M60" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>89</v>
       </c>
       <c r="N60" s="9"/>
@@ -7799,24 +7952,24 @@
         <v>79.600000000000023</v>
       </c>
       <c r="T60" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17.8</v>
       </c>
       <c r="U60" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.5999999999999943</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" si="6"/>
         <v>6.5999999999999943</v>
       </c>
-      <c r="W60" s="19"/>
+      <c r="W60" s="9"/>
       <c r="X60" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="Y60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.629213483146067</v>
       </c>
       <c r="Z60" s="9">
@@ -7854,7 +8007,10 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AL60" s="9"/>
+      <c r="AL60" s="9">
+        <f t="shared" si="9"/>
+        <v>11.763636363636364</v>
+      </c>
       <c r="AM60" s="9"/>
       <c r="AN60" s="9"/>
       <c r="AO60" s="9"/>
@@ -7897,11 +8053,11 @@
         <v>7</v>
       </c>
       <c r="L61" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M61" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="N61" s="9"/>
@@ -7915,7 +8071,7 @@
         <v>9.7999999999999972</v>
       </c>
       <c r="T61" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.4</v>
       </c>
       <c r="U61" s="4"/>
@@ -7923,13 +8079,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W61" s="19"/>
+      <c r="W61" s="9"/>
       <c r="X61" s="9">
         <f t="shared" si="7"/>
         <v>19.142857142857142</v>
       </c>
       <c r="Y61" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>19.142857142857142</v>
       </c>
       <c r="Z61" s="9">
@@ -7967,7 +8123,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL61" s="9"/>
+      <c r="AL61" s="9">
+        <f t="shared" si="9"/>
+        <v>2.0363636363636366</v>
+      </c>
       <c r="AM61" s="9"/>
       <c r="AN61" s="9"/>
       <c r="AO61" s="9"/>
@@ -8012,11 +8171,11 @@
         <v>90.9</v>
       </c>
       <c r="L62" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.6009999999999991</v>
       </c>
       <c r="M62" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>83.299000000000007</v>
       </c>
       <c r="N62" s="9"/>
@@ -8030,24 +8189,24 @@
         <v>26.341400000000011</v>
       </c>
       <c r="T62" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.659800000000001</v>
       </c>
       <c r="U62" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>22.400199999999998</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" si="6"/>
         <v>22.400199999999998</v>
       </c>
-      <c r="W62" s="19"/>
+      <c r="W62" s="9"/>
       <c r="X62" s="9">
         <f t="shared" si="7"/>
         <v>10.999999999999998</v>
       </c>
       <c r="Y62" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.6554340388239943</v>
       </c>
       <c r="Z62" s="9">
@@ -8085,7 +8244,10 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="AL62" s="9"/>
+      <c r="AL62" s="9">
+        <f t="shared" si="9"/>
+        <v>13.369254545454544</v>
+      </c>
       <c r="AM62" s="9"/>
       <c r="AN62" s="9"/>
       <c r="AO62" s="9"/>
@@ -8130,11 +8292,11 @@
         <v>24.167000000000002</v>
       </c>
       <c r="L63" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.8960000000000008</v>
       </c>
       <c r="M63" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23.271000000000001</v>
       </c>
       <c r="N63" s="9"/>
@@ -8148,7 +8310,7 @@
         <v>70</v>
       </c>
       <c r="T63" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.6542000000000003</v>
       </c>
       <c r="U63" s="4"/>
@@ -8156,13 +8318,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W63" s="19"/>
+      <c r="W63" s="9"/>
       <c r="X63" s="9">
         <f t="shared" si="7"/>
         <v>18.439044304069441</v>
       </c>
       <c r="Y63" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.439044304069441</v>
       </c>
       <c r="Z63" s="9">
@@ -8202,7 +8364,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL63" s="9"/>
+      <c r="AL63" s="9">
+        <f t="shared" si="9"/>
+        <v>4.8971454545454556</v>
+      </c>
       <c r="AM63" s="9"/>
       <c r="AN63" s="9"/>
       <c r="AO63" s="9"/>
@@ -8247,11 +8412,11 @@
         <v>461</v>
       </c>
       <c r="L64" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-12</v>
       </c>
       <c r="M64" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>449</v>
       </c>
       <c r="N64" s="9"/>
@@ -8265,7 +8430,7 @@
         <v>478.04600000000028</v>
       </c>
       <c r="T64" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>89.8</v>
       </c>
       <c r="U64" s="4"/>
@@ -8273,13 +8438,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W64" s="19"/>
+      <c r="W64" s="9"/>
       <c r="X64" s="9">
         <f t="shared" si="7"/>
         <v>13.400824053452121</v>
       </c>
       <c r="Y64" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.400824053452121</v>
       </c>
       <c r="Z64" s="9">
@@ -8317,7 +8482,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL64" s="9"/>
+      <c r="AL64" s="9">
+        <f t="shared" si="9"/>
+        <v>73.563636363636363</v>
+      </c>
       <c r="AM64" s="9"/>
       <c r="AN64" s="9"/>
       <c r="AO64" s="9"/>
@@ -8362,11 +8530,11 @@
         <v>45</v>
       </c>
       <c r="L65" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-15</v>
       </c>
       <c r="M65" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="N65" s="9"/>
@@ -8382,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="U65" s="4"/>
@@ -8390,13 +8558,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W65" s="19"/>
+      <c r="W65" s="9"/>
       <c r="X65" s="9">
         <f t="shared" si="7"/>
         <v>79.333333333333329</v>
       </c>
       <c r="Y65" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>79.333333333333329</v>
       </c>
       <c r="Z65" s="9">
@@ -8434,7 +8602,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL65" s="9"/>
+      <c r="AL65" s="9">
+        <f t="shared" si="9"/>
+        <v>55.56363636363637</v>
+      </c>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
       <c r="AO65" s="9"/>
@@ -8479,11 +8650,11 @@
         <v>110.4</v>
       </c>
       <c r="L66" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3289999999999935</v>
       </c>
       <c r="M66" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>111.729</v>
       </c>
       <c r="N66" s="9"/>
@@ -8497,7 +8668,7 @@
         <v>82.244400000000013</v>
       </c>
       <c r="T66" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.345800000000001</v>
       </c>
       <c r="U66" s="4"/>
@@ -8505,13 +8676,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W66" s="19"/>
+      <c r="W66" s="9"/>
       <c r="X66" s="9">
         <f t="shared" si="7"/>
         <v>14.316945466262114</v>
       </c>
       <c r="Y66" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.316945466262114</v>
       </c>
       <c r="Z66" s="9">
@@ -8549,7 +8720,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL66" s="9"/>
+      <c r="AL66" s="9">
+        <f t="shared" si="9"/>
+        <v>30.725945454545457</v>
+      </c>
       <c r="AM66" s="9"/>
       <c r="AN66" s="9"/>
       <c r="AO66" s="9"/>
@@ -8594,11 +8768,11 @@
         <v>100.3</v>
       </c>
       <c r="L67" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.1140000000000043</v>
       </c>
       <c r="M67" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>103.414</v>
       </c>
       <c r="N67" s="9"/>
@@ -8612,7 +8786,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.6828</v>
       </c>
       <c r="U67" s="4"/>
@@ -8620,13 +8794,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W67" s="19"/>
+      <c r="W67" s="9"/>
       <c r="X67" s="9">
         <f t="shared" si="7"/>
         <v>13.656922660374804</v>
       </c>
       <c r="Y67" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.656922660374804</v>
       </c>
       <c r="Z67" s="9">
@@ -8664,7 +8838,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL67" s="9"/>
+      <c r="AL67" s="9">
+        <f t="shared" si="9"/>
+        <v>27.621327272727271</v>
+      </c>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
       <c r="AO67" s="9"/>
@@ -8709,11 +8886,11 @@
         <v>274.11599999999999</v>
       </c>
       <c r="L68" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5.325999999999965</v>
       </c>
       <c r="M68" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>268.79000000000002</v>
       </c>
       <c r="N68" s="9"/>
@@ -8727,7 +8904,7 @@
         <v>14.14059399999978</v>
       </c>
       <c r="T68" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>53.758000000000003</v>
       </c>
       <c r="U68" s="4"/>
@@ -8735,13 +8912,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W68" s="19"/>
+      <c r="W68" s="9"/>
       <c r="X68" s="9">
         <f t="shared" si="7"/>
         <v>11.052871349380558</v>
       </c>
       <c r="Y68" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.052871349380558</v>
       </c>
       <c r="Z68" s="9">
@@ -8779,7 +8956,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="9"/>
+      <c r="AL68" s="9">
+        <f t="shared" si="9"/>
+        <v>74.508727272727285</v>
+      </c>
       <c r="AM68" s="9"/>
       <c r="AN68" s="9"/>
       <c r="AO68" s="9"/>
@@ -8824,11 +9004,11 @@
         <v>143.5</v>
       </c>
       <c r="L69" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.421999999999997</v>
       </c>
       <c r="M69" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>135.078</v>
       </c>
       <c r="N69" s="9"/>
@@ -8842,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>27.015599999999999</v>
       </c>
       <c r="U69" s="4"/>
@@ -8850,13 +9030,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W69" s="19"/>
+      <c r="W69" s="9"/>
       <c r="X69" s="9">
         <f t="shared" si="7"/>
         <v>14.238477028087475</v>
       </c>
       <c r="Y69" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.238477028087475</v>
       </c>
       <c r="Z69" s="9">
@@ -8894,7 +9074,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="9"/>
+      <c r="AL69" s="9">
+        <f t="shared" si="9"/>
+        <v>33.777581818181822</v>
+      </c>
       <c r="AM69" s="9"/>
       <c r="AN69" s="9"/>
       <c r="AO69" s="9"/>
@@ -8927,11 +9110,11 @@
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11">
-        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="17">E70-K70</f>
         <v>0</v>
       </c>
       <c r="M70" s="11">
-        <f t="shared" ref="M70:M101" si="17">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="18">E70-N70</f>
         <v>0</v>
       </c>
       <c r="N70" s="11"/>
@@ -8945,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="11">
-        <f t="shared" ref="T70:T101" si="18">M70/5</f>
+        <f t="shared" ref="T70:T101" si="19">M70/5</f>
         <v>0</v>
       </c>
       <c r="U70" s="13"/>
@@ -8953,13 +9136,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W70" s="20"/>
+      <c r="W70" s="11"/>
       <c r="X70" s="9" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y70" s="11" t="e">
-        <f t="shared" ref="Y70:Y101" si="19">(F70+O70+P70+Q70+R70+S70)/T70</f>
+        <f t="shared" ref="Y70:Y101" si="20">(F70+O70+P70+Q70+R70+S70)/T70</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z70" s="11">
@@ -8999,7 +9182,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL70" s="9"/>
+      <c r="AL70" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM70" s="9"/>
       <c r="AN70" s="9"/>
       <c r="AO70" s="9"/>
@@ -9044,11 +9230,11 @@
         <v>142.54599999999999</v>
       </c>
       <c r="L71" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-35.184999999999988</v>
       </c>
       <c r="M71" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>107.361</v>
       </c>
       <c r="N71" s="9"/>
@@ -9062,21 +9248,21 @@
         <v>4</v>
       </c>
       <c r="T71" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21.472200000000001</v>
       </c>
       <c r="U71" s="4"/>
       <c r="V71" s="4">
-        <f t="shared" ref="V71:V131" si="20">U71</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="19"/>
+        <f t="shared" ref="V71:V131" si="21">U71</f>
+        <v>0</v>
+      </c>
+      <c r="W71" s="9"/>
       <c r="X71" s="9">
-        <f t="shared" ref="X71:X131" si="21">(F71+O71+P71+Q71+R71+S71+V71)/T71</f>
+        <f t="shared" ref="X71:X131" si="22">(F71+O71+P71+Q71+R71+S71+V71)/T71</f>
         <v>12.006361714216521</v>
       </c>
       <c r="Y71" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.006361714216521</v>
       </c>
       <c r="Z71" s="9">
@@ -9111,10 +9297,13 @@
       </c>
       <c r="AJ71" s="9"/>
       <c r="AK71" s="9">
-        <f t="shared" ref="AK71:AK131" si="22">ROUND(G71*V71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL71" s="9"/>
+        <f t="shared" ref="AK71:AK131" si="23">ROUND(G71*V71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="9">
+        <f t="shared" ref="AL71:AL131" si="24">(SUM(Z71:AI71)+T71)/11</f>
+        <v>37.20065454545454</v>
+      </c>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
       <c r="AO71" s="9"/>
@@ -9159,11 +9348,11 @@
         <v>119</v>
       </c>
       <c r="L72" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>16</v>
       </c>
       <c r="M72" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>135</v>
       </c>
       <c r="N72" s="9"/>
@@ -9177,24 +9366,24 @@
         <v>179.4</v>
       </c>
       <c r="T72" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>27</v>
       </c>
       <c r="U72" s="4">
-        <f t="shared" ref="U72" si="23">11*T72-S72-R72-Q72-P72-O72-F72</f>
+        <f t="shared" ref="U72" si="25">11*T72-S72-R72-Q72-P72-O72-F72</f>
         <v>65.599999999999994</v>
       </c>
       <c r="V72" s="4">
+        <f t="shared" si="21"/>
+        <v>65.599999999999994</v>
+      </c>
+      <c r="W72" s="9"/>
+      <c r="X72" s="9">
+        <f t="shared" si="22"/>
+        <v>11</v>
+      </c>
+      <c r="Y72" s="9">
         <f t="shared" si="20"/>
-        <v>65.599999999999994</v>
-      </c>
-      <c r="W72" s="19"/>
-      <c r="X72" s="9">
-        <f t="shared" si="21"/>
-        <v>11</v>
-      </c>
-      <c r="Y72" s="9">
-        <f t="shared" si="19"/>
         <v>8.5703703703703713</v>
       </c>
       <c r="Z72" s="9">
@@ -9229,10 +9418,13 @@
       </c>
       <c r="AJ72" s="9"/>
       <c r="AK72" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>39</v>
       </c>
-      <c r="AL72" s="9"/>
+      <c r="AL72" s="9">
+        <f t="shared" si="24"/>
+        <v>18.927272727272726</v>
+      </c>
       <c r="AM72" s="9"/>
       <c r="AN72" s="9"/>
       <c r="AO72" s="9"/>
@@ -9277,11 +9469,11 @@
         <v>123</v>
       </c>
       <c r="L73" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10</v>
       </c>
       <c r="M73" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>133</v>
       </c>
       <c r="N73" s="9"/>
@@ -9295,21 +9487,21 @@
         <v>123.2</v>
       </c>
       <c r="T73" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26.6</v>
       </c>
       <c r="U73" s="4"/>
       <c r="V73" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W73" s="9"/>
+      <c r="X73" s="9">
+        <f t="shared" si="22"/>
+        <v>18.394360902255634</v>
+      </c>
+      <c r="Y73" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W73" s="19"/>
-      <c r="X73" s="9">
-        <f t="shared" si="21"/>
-        <v>18.394360902255634</v>
-      </c>
-      <c r="Y73" s="9">
-        <f t="shared" si="19"/>
         <v>18.394360902255634</v>
       </c>
       <c r="Z73" s="9">
@@ -9344,10 +9536,13 @@
       </c>
       <c r="AJ73" s="9"/>
       <c r="AK73" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL73" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="9">
+        <f t="shared" si="24"/>
+        <v>33.927272727272729</v>
+      </c>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
       <c r="AO73" s="9"/>
@@ -9392,11 +9587,11 @@
         <v>78</v>
       </c>
       <c r="L74" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-10</v>
       </c>
       <c r="M74" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>68</v>
       </c>
       <c r="N74" s="9"/>
@@ -9410,21 +9605,21 @@
         <v>0</v>
       </c>
       <c r="T74" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.6</v>
       </c>
       <c r="U74" s="4"/>
       <c r="V74" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W74" s="9"/>
+      <c r="X74" s="9">
+        <f t="shared" si="22"/>
+        <v>15.338235294117649</v>
+      </c>
+      <c r="Y74" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W74" s="19"/>
-      <c r="X74" s="9">
-        <f t="shared" si="21"/>
-        <v>15.338235294117649</v>
-      </c>
-      <c r="Y74" s="9">
-        <f t="shared" si="19"/>
         <v>15.338235294117649</v>
       </c>
       <c r="Z74" s="9">
@@ -9459,10 +9654,13 @@
       </c>
       <c r="AJ74" s="9"/>
       <c r="AK74" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL74" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL74" s="9">
+        <f t="shared" si="24"/>
+        <v>21.490909090909096</v>
+      </c>
       <c r="AM74" s="9"/>
       <c r="AN74" s="9"/>
       <c r="AO74" s="9"/>
@@ -9507,11 +9705,11 @@
         <v>129</v>
       </c>
       <c r="L75" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M75" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>124</v>
       </c>
       <c r="N75" s="9"/>
@@ -9525,21 +9723,21 @@
         <v>111.03999999999979</v>
       </c>
       <c r="T75" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>24.8</v>
       </c>
       <c r="U75" s="4"/>
       <c r="V75" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W75" s="9"/>
+      <c r="X75" s="9">
+        <f t="shared" si="22"/>
+        <v>12.451612903225797</v>
+      </c>
+      <c r="Y75" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W75" s="19"/>
-      <c r="X75" s="9">
-        <f t="shared" si="21"/>
-        <v>12.451612903225797</v>
-      </c>
-      <c r="Y75" s="9">
-        <f t="shared" si="19"/>
         <v>12.451612903225797</v>
       </c>
       <c r="Z75" s="9">
@@ -9574,10 +9772,13 @@
       </c>
       <c r="AJ75" s="9"/>
       <c r="AK75" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL75" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL75" s="9">
+        <f t="shared" si="24"/>
+        <v>28.472727272727273</v>
+      </c>
       <c r="AM75" s="9"/>
       <c r="AN75" s="9"/>
       <c r="AO75" s="9"/>
@@ -9622,11 +9823,11 @@
         <v>117</v>
       </c>
       <c r="L76" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M76" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>109</v>
       </c>
       <c r="N76" s="9"/>
@@ -9640,21 +9841,21 @@
         <v>71.200000000000102</v>
       </c>
       <c r="T76" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21.8</v>
       </c>
       <c r="U76" s="4"/>
       <c r="V76" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W76" s="9"/>
+      <c r="X76" s="9">
+        <f t="shared" si="22"/>
+        <v>12.165137614678903</v>
+      </c>
+      <c r="Y76" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W76" s="19"/>
-      <c r="X76" s="9">
-        <f t="shared" si="21"/>
-        <v>12.165137614678903</v>
-      </c>
-      <c r="Y76" s="9">
-        <f t="shared" si="19"/>
         <v>12.165137614678903</v>
       </c>
       <c r="Z76" s="9">
@@ -9689,10 +9890,13 @@
       </c>
       <c r="AJ76" s="9"/>
       <c r="AK76" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL76" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL76" s="9">
+        <f t="shared" si="24"/>
+        <v>27.963636363636365</v>
+      </c>
       <c r="AM76" s="9"/>
       <c r="AN76" s="9"/>
       <c r="AO76" s="9"/>
@@ -9727,11 +9931,11 @@
         <v>16</v>
       </c>
       <c r="L77" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-16</v>
       </c>
       <c r="M77" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N77" s="11"/>
@@ -9745,21 +9949,21 @@
         <v>0</v>
       </c>
       <c r="T77" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U77" s="13"/>
       <c r="V77" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W77" s="11"/>
+      <c r="X77" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y77" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W77" s="20"/>
-      <c r="X77" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y77" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z77" s="11">
@@ -9796,10 +10000,13 @@
         <v>47</v>
       </c>
       <c r="AK77" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL77" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM77" s="9"/>
       <c r="AN77" s="9"/>
       <c r="AO77" s="9"/>
@@ -9842,11 +10049,11 @@
         <v>29</v>
       </c>
       <c r="L78" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-14</v>
       </c>
       <c r="M78" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15</v>
       </c>
       <c r="N78" s="9"/>
@@ -9860,21 +10067,21 @@
         <v>0</v>
       </c>
       <c r="T78" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="U78" s="4"/>
       <c r="V78" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W78" s="9"/>
+      <c r="X78" s="9">
+        <f t="shared" si="22"/>
+        <v>77.2</v>
+      </c>
+      <c r="Y78" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W78" s="19"/>
-      <c r="X78" s="9">
-        <f t="shared" si="21"/>
-        <v>77.2</v>
-      </c>
-      <c r="Y78" s="9">
-        <f t="shared" si="19"/>
         <v>77.2</v>
       </c>
       <c r="Z78" s="9">
@@ -9909,10 +10116,13 @@
       </c>
       <c r="AJ78" s="9"/>
       <c r="AK78" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL78" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL78" s="9">
+        <f t="shared" si="24"/>
+        <v>12.799999999999999</v>
+      </c>
       <c r="AM78" s="9"/>
       <c r="AN78" s="9"/>
       <c r="AO78" s="9"/>
@@ -9955,11 +10165,11 @@
         <v>55</v>
       </c>
       <c r="L79" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M79" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>54</v>
       </c>
       <c r="N79" s="9"/>
@@ -9973,24 +10183,24 @@
         <v>0</v>
       </c>
       <c r="T79" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.8</v>
       </c>
       <c r="U79" s="4">
-        <f t="shared" ref="U79" si="24">11*T79-S79-R79-Q79-P79-O79-F79</f>
+        <f t="shared" ref="U79" si="26">11*T79-S79-R79-Q79-P79-O79-F79</f>
         <v>68.2</v>
       </c>
       <c r="V79" s="4">
+        <f t="shared" si="21"/>
+        <v>68.2</v>
+      </c>
+      <c r="W79" s="9"/>
+      <c r="X79" s="9">
+        <f t="shared" si="22"/>
+        <v>11</v>
+      </c>
+      <c r="Y79" s="9">
         <f t="shared" si="20"/>
-        <v>68.2</v>
-      </c>
-      <c r="W79" s="19"/>
-      <c r="X79" s="9">
-        <f t="shared" si="21"/>
-        <v>11</v>
-      </c>
-      <c r="Y79" s="9">
-        <f t="shared" si="19"/>
         <v>4.685185185185186</v>
       </c>
       <c r="Z79" s="9">
@@ -10025,10 +10235,13 @@
       </c>
       <c r="AJ79" s="9"/>
       <c r="AK79" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
-      <c r="AL79" s="9"/>
+      <c r="AL79" s="9">
+        <f t="shared" si="24"/>
+        <v>10.872727272727273</v>
+      </c>
       <c r="AM79" s="9"/>
       <c r="AN79" s="9"/>
       <c r="AO79" s="9"/>
@@ -10073,11 +10286,11 @@
         <v>38</v>
       </c>
       <c r="L80" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M80" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="N80" s="9"/>
@@ -10091,21 +10304,21 @@
         <v>0</v>
       </c>
       <c r="T80" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="U80" s="4"/>
       <c r="V80" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W80" s="9"/>
+      <c r="X80" s="9">
+        <f t="shared" si="22"/>
+        <v>13.166666666666666</v>
+      </c>
+      <c r="Y80" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W80" s="19"/>
-      <c r="X80" s="9">
-        <f t="shared" si="21"/>
-        <v>13.166666666666666</v>
-      </c>
-      <c r="Y80" s="9">
-        <f t="shared" si="19"/>
         <v>13.166666666666666</v>
       </c>
       <c r="Z80" s="9">
@@ -10140,10 +10353,13 @@
       </c>
       <c r="AJ80" s="9"/>
       <c r="AK80" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL80" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL80" s="9">
+        <f t="shared" si="24"/>
+        <v>7.4</v>
+      </c>
       <c r="AM80" s="9"/>
       <c r="AN80" s="9"/>
       <c r="AO80" s="9"/>
@@ -10188,11 +10404,11 @@
         <v>20</v>
       </c>
       <c r="L81" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M81" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20</v>
       </c>
       <c r="N81" s="9"/>
@@ -10206,21 +10422,21 @@
         <v>0</v>
       </c>
       <c r="T81" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="U81" s="4"/>
       <c r="V81" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W81" s="9"/>
+      <c r="X81" s="9">
+        <f t="shared" si="22"/>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Y81" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W81" s="19"/>
-      <c r="X81" s="9">
-        <f t="shared" si="21"/>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="Y81" s="9">
-        <f t="shared" si="19"/>
         <v>16.399999999999999</v>
       </c>
       <c r="Z81" s="9">
@@ -10255,10 +10471,13 @@
       </c>
       <c r="AJ81" s="9"/>
       <c r="AK81" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL81" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="9">
+        <f t="shared" si="24"/>
+        <v>5.5454545454545459</v>
+      </c>
       <c r="AM81" s="9"/>
       <c r="AN81" s="9"/>
       <c r="AO81" s="9"/>
@@ -10303,11 +10522,11 @@
         <v>137</v>
       </c>
       <c r="L82" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-63</v>
       </c>
       <c r="M82" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>74</v>
       </c>
       <c r="N82" s="9"/>
@@ -10321,21 +10540,21 @@
         <v>0</v>
       </c>
       <c r="T82" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.8</v>
       </c>
       <c r="U82" s="4"/>
       <c r="V82" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W82" s="9"/>
+      <c r="X82" s="9">
+        <f t="shared" si="22"/>
+        <v>16.148648648648649</v>
+      </c>
+      <c r="Y82" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W82" s="19"/>
-      <c r="X82" s="9">
-        <f t="shared" si="21"/>
-        <v>16.148648648648649</v>
-      </c>
-      <c r="Y82" s="9">
-        <f t="shared" si="19"/>
         <v>16.148648648648649</v>
       </c>
       <c r="Z82" s="9">
@@ -10370,10 +10589,13 @@
       </c>
       <c r="AJ82" s="9"/>
       <c r="AK82" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL82" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL82" s="9">
+        <f t="shared" si="24"/>
+        <v>29.127272727272729</v>
+      </c>
       <c r="AM82" s="9"/>
       <c r="AN82" s="9"/>
       <c r="AO82" s="9"/>
@@ -10406,11 +10628,11 @@
       <c r="J83" s="11"/>
       <c r="K83" s="11"/>
       <c r="L83" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M83" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N83" s="11"/>
@@ -10424,21 +10646,21 @@
         <v>0</v>
       </c>
       <c r="T83" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U83" s="13"/>
       <c r="V83" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W83" s="11"/>
+      <c r="X83" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y83" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W83" s="20"/>
-      <c r="X83" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y83" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z83" s="11">
@@ -10475,10 +10697,13 @@
         <v>47</v>
       </c>
       <c r="AK83" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL83" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL83" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM83" s="9"/>
       <c r="AN83" s="9"/>
       <c r="AO83" s="9"/>
@@ -10511,11 +10736,11 @@
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
       <c r="L84" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M84" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N84" s="11"/>
@@ -10529,21 +10754,21 @@
         <v>0</v>
       </c>
       <c r="T84" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U84" s="13"/>
       <c r="V84" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W84" s="11"/>
+      <c r="X84" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y84" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W84" s="20"/>
-      <c r="X84" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y84" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z84" s="11">
@@ -10580,10 +10805,13 @@
         <v>47</v>
       </c>
       <c r="AK84" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL84" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL84" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM84" s="9"/>
       <c r="AN84" s="9"/>
       <c r="AO84" s="9"/>
@@ -10616,11 +10844,11 @@
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
       <c r="L85" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M85" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N85" s="11"/>
@@ -10634,21 +10862,21 @@
         <v>0</v>
       </c>
       <c r="T85" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U85" s="13"/>
       <c r="V85" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W85" s="11"/>
+      <c r="X85" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y85" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W85" s="20"/>
-      <c r="X85" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y85" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z85" s="11">
@@ -10685,10 +10913,13 @@
         <v>47</v>
       </c>
       <c r="AK85" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL85" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL85" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM85" s="9"/>
       <c r="AN85" s="9"/>
       <c r="AO85" s="9"/>
@@ -10733,11 +10964,11 @@
         <v>119.7</v>
       </c>
       <c r="L86" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.37199999999999989</v>
       </c>
       <c r="M86" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>119.328</v>
       </c>
       <c r="N86" s="9"/>
@@ -10751,21 +10982,21 @@
         <v>0</v>
       </c>
       <c r="T86" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>23.865600000000001</v>
       </c>
       <c r="U86" s="4"/>
       <c r="V86" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W86" s="9"/>
+      <c r="X86" s="9">
+        <f t="shared" si="22"/>
+        <v>17.544624899436847</v>
+      </c>
+      <c r="Y86" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W86" s="19"/>
-      <c r="X86" s="9">
-        <f t="shared" si="21"/>
-        <v>17.544624899436847</v>
-      </c>
-      <c r="Y86" s="9">
-        <f t="shared" si="19"/>
         <v>17.544624899436847</v>
       </c>
       <c r="Z86" s="9">
@@ -10800,10 +11031,13 @@
       </c>
       <c r="AJ86" s="9"/>
       <c r="AK86" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL86" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL86" s="9">
+        <f t="shared" si="24"/>
+        <v>39.687909090909095</v>
+      </c>
       <c r="AM86" s="9"/>
       <c r="AN86" s="9"/>
       <c r="AO86" s="9"/>
@@ -10836,11 +11070,11 @@
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M87" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N87" s="11"/>
@@ -10854,21 +11088,21 @@
         <v>0</v>
       </c>
       <c r="T87" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U87" s="13"/>
       <c r="V87" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W87" s="11"/>
+      <c r="X87" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y87" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W87" s="20"/>
-      <c r="X87" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y87" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z87" s="11">
@@ -10905,10 +11139,13 @@
         <v>47</v>
       </c>
       <c r="AK87" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL87" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL87" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM87" s="9"/>
       <c r="AN87" s="9"/>
       <c r="AO87" s="9"/>
@@ -10953,11 +11190,11 @@
         <v>1247.1469999999999</v>
       </c>
       <c r="L88" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-30.993999999999915</v>
       </c>
       <c r="M88" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>961.50600000000009</v>
       </c>
       <c r="N88" s="9">
@@ -10973,21 +11210,21 @@
         <v>0</v>
       </c>
       <c r="T88" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>192.30120000000002</v>
       </c>
       <c r="U88" s="4"/>
       <c r="V88" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W88" s="9"/>
+      <c r="X88" s="9">
+        <f t="shared" si="22"/>
+        <v>14.409265256795067</v>
+      </c>
+      <c r="Y88" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W88" s="19"/>
-      <c r="X88" s="9">
-        <f t="shared" si="21"/>
-        <v>14.409265256795067</v>
-      </c>
-      <c r="Y88" s="9">
-        <f t="shared" si="19"/>
         <v>14.409265256795067</v>
       </c>
       <c r="Z88" s="9">
@@ -11022,10 +11259,13 @@
       </c>
       <c r="AJ88" s="9"/>
       <c r="AK88" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL88" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL88" s="9">
+        <f t="shared" si="24"/>
+        <v>289.71340000000004</v>
+      </c>
       <c r="AM88" s="9"/>
       <c r="AN88" s="9"/>
       <c r="AO88" s="9"/>
@@ -11070,11 +11310,11 @@
         <v>854.43299999999999</v>
       </c>
       <c r="L89" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-30.836000000000013</v>
       </c>
       <c r="M89" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>615.16399999999999</v>
       </c>
       <c r="N89" s="9">
@@ -11094,21 +11334,21 @@
         <v>0</v>
       </c>
       <c r="T89" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>123.03279999999999</v>
       </c>
       <c r="U89" s="4"/>
       <c r="V89" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W89" s="9"/>
+      <c r="X89" s="9">
+        <f t="shared" si="22"/>
+        <v>24.26622542931641</v>
+      </c>
+      <c r="Y89" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W89" s="19"/>
-      <c r="X89" s="9">
-        <f t="shared" si="21"/>
-        <v>24.26622542931641</v>
-      </c>
-      <c r="Y89" s="9">
-        <f t="shared" si="19"/>
         <v>24.26622542931641</v>
       </c>
       <c r="Z89" s="9">
@@ -11145,10 +11385,13 @@
         <v>58</v>
       </c>
       <c r="AK89" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL89" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL89" s="9">
+        <f t="shared" si="24"/>
+        <v>227.17130909090909</v>
+      </c>
       <c r="AM89" s="9"/>
       <c r="AN89" s="9"/>
       <c r="AO89" s="9"/>
@@ -11193,11 +11436,11 @@
         <v>1905.7429999999999</v>
       </c>
       <c r="L90" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-54.351999999999862</v>
       </c>
       <c r="M90" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1597.1480000000001</v>
       </c>
       <c r="N90" s="9">
@@ -11217,21 +11460,21 @@
         <v>492.90262599999909</v>
       </c>
       <c r="T90" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>319.42960000000005</v>
       </c>
       <c r="U90" s="4"/>
       <c r="V90" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W90" s="9"/>
+      <c r="X90" s="9">
+        <f t="shared" si="22"/>
+        <v>16.951229648097726</v>
+      </c>
+      <c r="Y90" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W90" s="19"/>
-      <c r="X90" s="9">
-        <f t="shared" si="21"/>
-        <v>16.951229648097726</v>
-      </c>
-      <c r="Y90" s="9">
-        <f t="shared" si="19"/>
         <v>16.951229648097726</v>
       </c>
       <c r="Z90" s="9">
@@ -11266,10 +11509,13 @@
       </c>
       <c r="AJ90" s="9"/>
       <c r="AK90" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL90" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL90" s="9">
+        <f t="shared" si="24"/>
+        <v>396.44503636363629</v>
+      </c>
       <c r="AM90" s="9"/>
       <c r="AN90" s="9"/>
       <c r="AO90" s="9"/>
@@ -11302,11 +11548,11 @@
       <c r="J91" s="11"/>
       <c r="K91" s="11"/>
       <c r="L91" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M91" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N91" s="11"/>
@@ -11320,21 +11566,21 @@
         <v>0</v>
       </c>
       <c r="T91" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U91" s="13"/>
       <c r="V91" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W91" s="11"/>
+      <c r="X91" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y91" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W91" s="20"/>
-      <c r="X91" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y91" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z91" s="11">
@@ -11371,10 +11617,13 @@
         <v>47</v>
       </c>
       <c r="AK91" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL91" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM91" s="9"/>
       <c r="AN91" s="9"/>
       <c r="AO91" s="9"/>
@@ -11419,11 +11668,11 @@
         <v>76</v>
       </c>
       <c r="L92" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-15</v>
       </c>
       <c r="M92" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>61</v>
       </c>
       <c r="N92" s="9"/>
@@ -11437,21 +11686,21 @@
         <v>0</v>
       </c>
       <c r="T92" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.2</v>
       </c>
       <c r="U92" s="4"/>
       <c r="V92" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W92" s="9"/>
+      <c r="X92" s="9">
+        <f t="shared" si="22"/>
+        <v>13.377049180327869</v>
+      </c>
+      <c r="Y92" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W92" s="19"/>
-      <c r="X92" s="9">
-        <f t="shared" si="21"/>
-        <v>13.377049180327869</v>
-      </c>
-      <c r="Y92" s="9">
-        <f t="shared" si="19"/>
         <v>13.377049180327869</v>
       </c>
       <c r="Z92" s="9">
@@ -11486,10 +11735,13 @@
       </c>
       <c r="AJ92" s="9"/>
       <c r="AK92" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL92" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL92" s="9">
+        <f t="shared" si="24"/>
+        <v>21.127272727272722</v>
+      </c>
       <c r="AM92" s="9"/>
       <c r="AN92" s="9"/>
       <c r="AO92" s="9"/>
@@ -11522,11 +11774,11 @@
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
       <c r="L93" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M93" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N93" s="11"/>
@@ -11540,21 +11792,21 @@
         <v>0</v>
       </c>
       <c r="T93" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U93" s="13"/>
       <c r="V93" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W93" s="11"/>
+      <c r="X93" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y93" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W93" s="20"/>
-      <c r="X93" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y93" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z93" s="11">
@@ -11591,10 +11843,13 @@
         <v>47</v>
       </c>
       <c r="AK93" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL93" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL93" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM93" s="9"/>
       <c r="AN93" s="9"/>
       <c r="AO93" s="9"/>
@@ -11639,11 +11894,11 @@
         <v>55</v>
       </c>
       <c r="L94" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M94" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>54</v>
       </c>
       <c r="N94" s="9"/>
@@ -11657,7 +11912,7 @@
         <v>42.400000000000027</v>
       </c>
       <c r="T94" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.8</v>
       </c>
       <c r="U94" s="4"/>
@@ -11665,15 +11920,15 @@
         <f>U94+W94</f>
         <v>80</v>
       </c>
-      <c r="W94" s="19">
+      <c r="W94" s="9">
         <v>80</v>
       </c>
       <c r="X94" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29.148148148148152</v>
       </c>
       <c r="Y94" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21.740740740740744</v>
       </c>
       <c r="Z94" s="9">
@@ -11710,10 +11965,13 @@
         <v>182</v>
       </c>
       <c r="AK94" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL94" s="9"/>
+      <c r="AL94" s="9">
+        <f t="shared" si="24"/>
+        <v>14.454545454545457</v>
+      </c>
       <c r="AM94" s="9"/>
       <c r="AN94" s="9"/>
       <c r="AO94" s="9"/>
@@ -11758,11 +12016,11 @@
         <v>99</v>
       </c>
       <c r="L95" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M95" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>94</v>
       </c>
       <c r="N95" s="9"/>
@@ -11776,7 +12034,7 @@
         <v>0</v>
       </c>
       <c r="T95" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.8</v>
       </c>
       <c r="U95" s="4">
@@ -11787,15 +12045,15 @@
         <f>U95+W95</f>
         <v>196.2</v>
       </c>
-      <c r="W95" s="19">
+      <c r="W95" s="9">
         <v>80</v>
       </c>
       <c r="X95" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14.25531914893617</v>
       </c>
       <c r="Y95" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.8191489361702131</v>
       </c>
       <c r="Z95" s="9">
@@ -11832,10 +12090,13 @@
         <v>182</v>
       </c>
       <c r="AK95" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14</v>
       </c>
-      <c r="AL95" s="9"/>
+      <c r="AL95" s="9">
+        <f t="shared" si="24"/>
+        <v>16.109090909090909</v>
+      </c>
       <c r="AM95" s="9"/>
       <c r="AN95" s="9"/>
       <c r="AO95" s="9"/>
@@ -11880,11 +12141,11 @@
         <v>56</v>
       </c>
       <c r="L96" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M96" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>50</v>
       </c>
       <c r="N96" s="9"/>
@@ -11898,7 +12159,7 @@
         <v>61.8</v>
       </c>
       <c r="T96" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="U96" s="4"/>
@@ -11906,15 +12167,15 @@
         <f>U96+W96</f>
         <v>80</v>
       </c>
-      <c r="W96" s="19">
+      <c r="W96" s="9">
         <v>80</v>
       </c>
       <c r="X96" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29.52</v>
       </c>
       <c r="Y96" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21.52</v>
       </c>
       <c r="Z96" s="9">
@@ -11951,10 +12212,13 @@
         <v>182</v>
       </c>
       <c r="AK96" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL96" s="9"/>
+      <c r="AL96" s="9">
+        <f t="shared" si="24"/>
+        <v>12.399999999999999</v>
+      </c>
       <c r="AM96" s="9"/>
       <c r="AN96" s="9"/>
       <c r="AO96" s="9"/>
@@ -11999,11 +12263,11 @@
         <v>44</v>
       </c>
       <c r="L97" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7</v>
       </c>
       <c r="M97" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="N97" s="11"/>
@@ -12017,21 +12281,21 @@
         <v>0</v>
       </c>
       <c r="T97" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.4</v>
       </c>
       <c r="U97" s="13"/>
       <c r="V97" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W97" s="11"/>
+      <c r="X97" s="9">
+        <f t="shared" si="22"/>
+        <v>16.891891891891891</v>
+      </c>
+      <c r="Y97" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W97" s="20"/>
-      <c r="X97" s="9">
-        <f t="shared" si="21"/>
-        <v>16.891891891891891</v>
-      </c>
-      <c r="Y97" s="11">
-        <f t="shared" si="19"/>
         <v>16.891891891891891</v>
       </c>
       <c r="Z97" s="11">
@@ -12068,10 +12332,13 @@
         <v>58</v>
       </c>
       <c r="AK97" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL97" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL97" s="9">
+        <f t="shared" si="24"/>
+        <v>13.454545454545455</v>
+      </c>
       <c r="AM97" s="9"/>
       <c r="AN97" s="9"/>
       <c r="AO97" s="9"/>
@@ -12104,11 +12371,11 @@
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
       <c r="L98" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M98" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N98" s="11"/>
@@ -12122,21 +12389,21 @@
         <v>0</v>
       </c>
       <c r="T98" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U98" s="13"/>
       <c r="V98" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W98" s="11"/>
+      <c r="X98" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y98" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W98" s="20"/>
-      <c r="X98" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y98" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z98" s="11">
@@ -12173,10 +12440,13 @@
         <v>47</v>
       </c>
       <c r="AK98" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL98" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL98" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM98" s="9"/>
       <c r="AN98" s="9"/>
       <c r="AO98" s="9"/>
@@ -12219,11 +12489,11 @@
         <v>9.4</v>
       </c>
       <c r="L99" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.6690000000000005</v>
       </c>
       <c r="M99" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.069000000000001</v>
       </c>
       <c r="N99" s="9"/>
@@ -12237,21 +12507,21 @@
         <v>0</v>
       </c>
       <c r="T99" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.2138</v>
       </c>
       <c r="U99" s="4"/>
       <c r="V99" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W99" s="9"/>
+      <c r="X99" s="9">
+        <f t="shared" si="22"/>
+        <v>29.852290179781374</v>
+      </c>
+      <c r="Y99" s="9">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W99" s="19"/>
-      <c r="X99" s="9">
-        <f t="shared" si="21"/>
-        <v>29.852290179781374</v>
-      </c>
-      <c r="Y99" s="9">
-        <f t="shared" si="19"/>
         <v>29.852290179781374</v>
       </c>
       <c r="Z99" s="9">
@@ -12288,10 +12558,13 @@
         <v>141</v>
       </c>
       <c r="AK99" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL99" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL99" s="9">
+        <f t="shared" si="24"/>
+        <v>11.642854545454547</v>
+      </c>
       <c r="AM99" s="9"/>
       <c r="AN99" s="9"/>
       <c r="AO99" s="9"/>
@@ -12332,11 +12605,11 @@
         <v>24</v>
       </c>
       <c r="L100" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M100" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16</v>
       </c>
       <c r="N100" s="9"/>
@@ -12350,7 +12623,7 @@
         <v>0</v>
       </c>
       <c r="T100" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.2</v>
       </c>
       <c r="U100" s="4">
@@ -12361,15 +12634,15 @@
         <f>U100+W100</f>
         <v>86</v>
       </c>
-      <c r="W100" s="19">
+      <c r="W100" s="9">
         <v>70</v>
       </c>
       <c r="X100" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>26.875</v>
       </c>
       <c r="Y100" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Z100" s="9">
@@ -12406,10 +12679,13 @@
         <v>180</v>
       </c>
       <c r="AK100" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9</v>
       </c>
-      <c r="AL100" s="9"/>
+      <c r="AL100" s="9">
+        <f t="shared" si="24"/>
+        <v>0.47272727272727272</v>
+      </c>
       <c r="AM100" s="9"/>
       <c r="AN100" s="9"/>
       <c r="AO100" s="9"/>
@@ -12442,11 +12718,11 @@
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
       <c r="L101" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M101" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N101" s="11"/>
@@ -12460,21 +12736,21 @@
         <v>0</v>
       </c>
       <c r="T101" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U101" s="13"/>
       <c r="V101" s="4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W101" s="11"/>
+      <c r="X101" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y101" s="11" t="e">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W101" s="20"/>
-      <c r="X101" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y101" s="11" t="e">
-        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z101" s="11">
@@ -12511,10 +12787,13 @@
         <v>47</v>
       </c>
       <c r="AK101" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL101" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL101" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM101" s="9"/>
       <c r="AN101" s="9"/>
       <c r="AO101" s="9"/>
@@ -12559,11 +12838,11 @@
         <v>107</v>
       </c>
       <c r="L102" s="9">
-        <f t="shared" ref="L102:L131" si="25">E102-K102</f>
+        <f t="shared" ref="L102:L131" si="27">E102-K102</f>
         <v>-20</v>
       </c>
       <c r="M102" s="9">
-        <f t="shared" ref="M102:M131" si="26">E102-N102</f>
+        <f t="shared" ref="M102:M131" si="28">E102-N102</f>
         <v>87</v>
       </c>
       <c r="N102" s="9"/>
@@ -12577,23 +12856,23 @@
         <v>81.599999999999994</v>
       </c>
       <c r="T102" s="9">
-        <f t="shared" ref="T102:T131" si="27">M102/5</f>
+        <f t="shared" ref="T102:T131" si="29">M102/5</f>
         <v>17.399999999999999</v>
       </c>
       <c r="U102" s="4"/>
       <c r="V102" s="4">
-        <f t="shared" ref="V102:V104" si="28">U102+W102</f>
+        <f t="shared" ref="V102:V104" si="30">U102+W102</f>
         <v>70</v>
       </c>
-      <c r="W102" s="19">
+      <c r="W102" s="9">
         <v>70</v>
       </c>
       <c r="X102" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18.919540229885058</v>
       </c>
       <c r="Y102" s="9">
-        <f t="shared" ref="Y102:Y131" si="29">(F102+O102+P102+Q102+R102+S102)/T102</f>
+        <f t="shared" ref="Y102:Y131" si="31">(F102+O102+P102+Q102+R102+S102)/T102</f>
         <v>14.896551724137932</v>
       </c>
       <c r="Z102" s="9">
@@ -12630,10 +12909,13 @@
         <v>180</v>
       </c>
       <c r="AK102" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL102" s="9"/>
+      <c r="AL102" s="9">
+        <f t="shared" si="24"/>
+        <v>18.872727272727271</v>
+      </c>
       <c r="AM102" s="9"/>
       <c r="AN102" s="9"/>
       <c r="AO102" s="9"/>
@@ -12678,11 +12960,11 @@
         <v>63</v>
       </c>
       <c r="L103" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-3</v>
       </c>
       <c r="M103" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="N103" s="9"/>
@@ -12696,23 +12978,23 @@
         <v>55</v>
       </c>
       <c r="T103" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12</v>
       </c>
       <c r="U103" s="4"/>
       <c r="V103" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>70</v>
       </c>
-      <c r="W103" s="19">
+      <c r="W103" s="9">
         <v>70</v>
       </c>
       <c r="X103" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19.583333333333332</v>
       </c>
       <c r="Y103" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.75</v>
       </c>
       <c r="Z103" s="9">
@@ -12749,10 +13031,13 @@
         <v>180</v>
       </c>
       <c r="AK103" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL103" s="9"/>
+      <c r="AL103" s="9">
+        <f t="shared" si="24"/>
+        <v>14.836363636363638</v>
+      </c>
       <c r="AM103" s="9"/>
       <c r="AN103" s="9"/>
       <c r="AO103" s="9"/>
@@ -12797,11 +13082,11 @@
         <v>17</v>
       </c>
       <c r="L104" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-13</v>
       </c>
       <c r="M104" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
       <c r="N104" s="9"/>
@@ -12815,23 +13100,23 @@
         <v>0</v>
       </c>
       <c r="T104" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.8</v>
       </c>
       <c r="U104" s="4"/>
       <c r="V104" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>70</v>
       </c>
-      <c r="W104" s="19">
+      <c r="W104" s="9">
         <v>70</v>
       </c>
       <c r="X104" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>105</v>
       </c>
       <c r="Y104" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>17.5</v>
       </c>
       <c r="Z104" s="9">
@@ -12868,10 +13153,13 @@
         <v>181</v>
       </c>
       <c r="AK104" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
-      <c r="AL104" s="9"/>
+      <c r="AL104" s="9">
+        <f t="shared" si="24"/>
+        <v>0.18181818181818182</v>
+      </c>
       <c r="AM104" s="9"/>
       <c r="AN104" s="9"/>
       <c r="AO104" s="9"/>
@@ -12916,11 +13204,11 @@
         <v>114.5</v>
       </c>
       <c r="L105" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-12.203999999999994</v>
       </c>
       <c r="M105" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>102.29600000000001</v>
       </c>
       <c r="N105" s="9"/>
@@ -12934,21 +13222,21 @@
         <v>0</v>
       </c>
       <c r="T105" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>20.459200000000003</v>
       </c>
       <c r="U105" s="4"/>
       <c r="V105" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W105" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W105" s="9"/>
       <c r="X105" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.841518729960114</v>
       </c>
       <c r="Y105" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.841518729960114</v>
       </c>
       <c r="Z105" s="9">
@@ -12983,10 +13271,13 @@
       </c>
       <c r="AJ105" s="9"/>
       <c r="AK105" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL105" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL105" s="9">
+        <f t="shared" si="24"/>
+        <v>29.318218181818182</v>
+      </c>
       <c r="AM105" s="9"/>
       <c r="AN105" s="9"/>
       <c r="AO105" s="9"/>
@@ -13031,11 +13322,11 @@
         <v>74.900000000000006</v>
       </c>
       <c r="L106" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-21.904000000000003</v>
       </c>
       <c r="M106" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>52.996000000000002</v>
       </c>
       <c r="N106" s="9"/>
@@ -13049,21 +13340,21 @@
         <v>0</v>
       </c>
       <c r="T106" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10.5992</v>
       </c>
       <c r="U106" s="4"/>
       <c r="V106" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W106" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W106" s="9"/>
       <c r="X106" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22.347535663068914</v>
       </c>
       <c r="Y106" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>22.347535663068914</v>
       </c>
       <c r="Z106" s="9">
@@ -13100,10 +13391,13 @@
         <v>58</v>
       </c>
       <c r="AK106" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL106" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="9">
+        <f t="shared" si="24"/>
+        <v>22.6968</v>
+      </c>
       <c r="AM106" s="9"/>
       <c r="AN106" s="9"/>
       <c r="AO106" s="9"/>
@@ -13148,11 +13442,11 @@
         <v>134.69999999999999</v>
       </c>
       <c r="L107" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-25.829999999999984</v>
       </c>
       <c r="M107" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>108.87</v>
       </c>
       <c r="N107" s="9"/>
@@ -13166,21 +13460,21 @@
         <v>101.3128000000001</v>
       </c>
       <c r="T107" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>21.774000000000001</v>
       </c>
       <c r="U107" s="4"/>
       <c r="V107" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W107" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W107" s="9"/>
       <c r="X107" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.834518232754666</v>
       </c>
       <c r="Y107" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.834518232754666</v>
       </c>
       <c r="Z107" s="9">
@@ -13215,10 +13509,13 @@
       </c>
       <c r="AJ107" s="9"/>
       <c r="AK107" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL107" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL107" s="9">
+        <f t="shared" si="24"/>
+        <v>15.272672727272726</v>
+      </c>
       <c r="AM107" s="9"/>
       <c r="AN107" s="9"/>
       <c r="AO107" s="9"/>
@@ -13251,11 +13548,11 @@
       <c r="J108" s="11"/>
       <c r="K108" s="11"/>
       <c r="L108" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M108" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N108" s="11"/>
@@ -13269,21 +13566,21 @@
         <v>0</v>
       </c>
       <c r="T108" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U108" s="13"/>
       <c r="V108" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W108" s="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W108" s="11"/>
       <c r="X108" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y108" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z108" s="11">
@@ -13320,10 +13617,13 @@
         <v>47</v>
       </c>
       <c r="AK108" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL108" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM108" s="9"/>
       <c r="AN108" s="9"/>
       <c r="AO108" s="9"/>
@@ -13356,11 +13656,11 @@
       <c r="J109" s="11"/>
       <c r="K109" s="11"/>
       <c r="L109" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M109" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N109" s="11"/>
@@ -13374,21 +13674,21 @@
         <v>0</v>
       </c>
       <c r="T109" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U109" s="13"/>
       <c r="V109" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W109" s="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W109" s="11"/>
       <c r="X109" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y109" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z109" s="11">
@@ -13425,10 +13725,13 @@
         <v>47</v>
       </c>
       <c r="AK109" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL109" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM109" s="9"/>
       <c r="AN109" s="9"/>
       <c r="AO109" s="9"/>
@@ -13473,11 +13776,11 @@
         <v>189</v>
       </c>
       <c r="L110" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-68</v>
       </c>
       <c r="M110" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>121</v>
       </c>
       <c r="N110" s="9"/>
@@ -13491,21 +13794,21 @@
         <v>0</v>
       </c>
       <c r="T110" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>24.2</v>
       </c>
       <c r="U110" s="4"/>
       <c r="V110" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W110" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W110" s="9"/>
       <c r="X110" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>21.652892561983471</v>
       </c>
       <c r="Y110" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>21.652892561983471</v>
       </c>
       <c r="Z110" s="9">
@@ -13542,10 +13845,13 @@
         <v>58</v>
       </c>
       <c r="AK110" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL110" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL110" s="9">
+        <f t="shared" si="24"/>
+        <v>44.218181818181819</v>
+      </c>
       <c r="AM110" s="9"/>
       <c r="AN110" s="9"/>
       <c r="AO110" s="9"/>
@@ -13590,11 +13896,11 @@
         <v>158</v>
       </c>
       <c r="L111" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-61</v>
       </c>
       <c r="M111" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>97</v>
       </c>
       <c r="N111" s="9"/>
@@ -13608,21 +13914,21 @@
         <v>0</v>
       </c>
       <c r="T111" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>19.399999999999999</v>
       </c>
       <c r="U111" s="4"/>
       <c r="V111" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W111" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W111" s="9"/>
       <c r="X111" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22.804123711340207</v>
       </c>
       <c r="Y111" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>22.804123711340207</v>
       </c>
       <c r="Z111" s="9">
@@ -13657,10 +13963,13 @@
       </c>
       <c r="AJ111" s="9"/>
       <c r="AK111" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL111" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL111" s="9">
+        <f t="shared" si="24"/>
+        <v>23.836363636363636</v>
+      </c>
       <c r="AM111" s="9"/>
       <c r="AN111" s="9"/>
       <c r="AO111" s="9"/>
@@ -13705,11 +14014,11 @@
         <v>222</v>
       </c>
       <c r="L112" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-56</v>
       </c>
       <c r="M112" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>166</v>
       </c>
       <c r="N112" s="9"/>
@@ -13723,21 +14032,21 @@
         <v>4.6999999999999602</v>
       </c>
       <c r="T112" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>33.200000000000003</v>
       </c>
       <c r="U112" s="4"/>
       <c r="V112" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W112" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W112" s="9"/>
       <c r="X112" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.707831325301202</v>
       </c>
       <c r="Y112" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.707831325301202</v>
       </c>
       <c r="Z112" s="9">
@@ -13772,10 +14081,13 @@
       </c>
       <c r="AJ112" s="9"/>
       <c r="AK112" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL112" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL112" s="9">
+        <f t="shared" si="24"/>
+        <v>41.472727272727276</v>
+      </c>
       <c r="AM112" s="9"/>
       <c r="AN112" s="9"/>
       <c r="AO112" s="9"/>
@@ -13820,11 +14132,11 @@
         <v>19</v>
       </c>
       <c r="L113" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="M113" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>18</v>
       </c>
       <c r="N113" s="9"/>
@@ -13838,7 +14150,7 @@
         <v>10</v>
       </c>
       <c r="T113" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.6</v>
       </c>
       <c r="U113" s="4"/>
@@ -13846,15 +14158,15 @@
         <f>U113+W113</f>
         <v>70</v>
       </c>
-      <c r="W113" s="19">
+      <c r="W113" s="9">
         <v>70</v>
       </c>
       <c r="X113" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>49.444444444444443</v>
       </c>
       <c r="Y113" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>30</v>
       </c>
       <c r="Z113" s="9">
@@ -13891,10 +14203,13 @@
         <v>180</v>
       </c>
       <c r="AK113" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL113" s="9"/>
+      <c r="AL113" s="9">
+        <f t="shared" si="24"/>
+        <v>5.1636363636363631</v>
+      </c>
       <c r="AM113" s="9"/>
       <c r="AN113" s="9"/>
       <c r="AO113" s="9"/>
@@ -13939,11 +14254,11 @@
         <v>42.5</v>
       </c>
       <c r="L114" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2.9669999999999987</v>
       </c>
       <c r="M114" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>39.533000000000001</v>
       </c>
       <c r="N114" s="9"/>
@@ -13957,21 +14272,21 @@
         <v>0</v>
       </c>
       <c r="T114" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>7.9066000000000001</v>
       </c>
       <c r="U114" s="4"/>
       <c r="V114" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W114" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W114" s="9"/>
       <c r="X114" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>24.963954164874913</v>
       </c>
       <c r="Y114" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>24.963954164874913</v>
       </c>
       <c r="Z114" s="9">
@@ -14008,10 +14323,13 @@
         <v>141</v>
       </c>
       <c r="AK114" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL114" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL114" s="9">
+        <f t="shared" si="24"/>
+        <v>12.198745454545456</v>
+      </c>
       <c r="AM114" s="9"/>
       <c r="AN114" s="9"/>
       <c r="AO114" s="9"/>
@@ -14056,11 +14374,11 @@
         <v>52.5</v>
       </c>
       <c r="L115" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-10.311999999999998</v>
       </c>
       <c r="M115" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>42.188000000000002</v>
       </c>
       <c r="N115" s="9"/>
@@ -14074,21 +14392,21 @@
         <v>0</v>
       </c>
       <c r="T115" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.4375999999999998</v>
       </c>
       <c r="U115" s="4"/>
       <c r="V115" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W115" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W115" s="9"/>
       <c r="X115" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>23.398122688916281</v>
       </c>
       <c r="Y115" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>23.398122688916281</v>
       </c>
       <c r="Z115" s="9">
@@ -14125,10 +14443,13 @@
         <v>141</v>
       </c>
       <c r="AK115" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL115" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL115" s="9">
+        <f t="shared" si="24"/>
+        <v>15.805272727272724</v>
+      </c>
       <c r="AM115" s="9"/>
       <c r="AN115" s="9"/>
       <c r="AO115" s="9"/>
@@ -14173,11 +14494,11 @@
         <v>33</v>
       </c>
       <c r="L116" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2</v>
       </c>
       <c r="M116" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="N116" s="9"/>
@@ -14191,23 +14512,23 @@
         <v>65.800000000000011</v>
       </c>
       <c r="T116" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6.2</v>
       </c>
       <c r="U116" s="4"/>
       <c r="V116" s="4">
-        <f t="shared" ref="V116:V117" si="30">U116+W116</f>
+        <f t="shared" ref="V116:V117" si="32">U116+W116</f>
         <v>70</v>
       </c>
-      <c r="W116" s="19">
+      <c r="W116" s="9">
         <v>70</v>
       </c>
       <c r="X116" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>28.516129032258064</v>
       </c>
       <c r="Y116" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>17.225806451612904</v>
       </c>
       <c r="Z116" s="9">
@@ -14244,10 +14565,13 @@
         <v>180</v>
       </c>
       <c r="AK116" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL116" s="9"/>
+      <c r="AL116" s="9">
+        <f t="shared" si="24"/>
+        <v>4.9272727272727277</v>
+      </c>
       <c r="AM116" s="9"/>
       <c r="AN116" s="9"/>
       <c r="AO116" s="9"/>
@@ -14292,11 +14616,11 @@
         <v>30</v>
       </c>
       <c r="L117" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2</v>
       </c>
       <c r="M117" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>28</v>
       </c>
       <c r="N117" s="9"/>
@@ -14310,23 +14634,23 @@
         <v>46.599999999999987</v>
       </c>
       <c r="T117" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.6</v>
       </c>
       <c r="U117" s="4"/>
       <c r="V117" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>70</v>
       </c>
-      <c r="W117" s="19">
+      <c r="W117" s="9">
         <v>70</v>
       </c>
       <c r="X117" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>27.964285714285715</v>
       </c>
       <c r="Y117" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.464285714285714</v>
       </c>
       <c r="Z117" s="9">
@@ -14363,10 +14687,13 @@
         <v>180</v>
       </c>
       <c r="AK117" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6</v>
       </c>
-      <c r="AL117" s="9"/>
+      <c r="AL117" s="9">
+        <f t="shared" si="24"/>
+        <v>4.5636363636363635</v>
+      </c>
       <c r="AM117" s="9"/>
       <c r="AN117" s="9"/>
       <c r="AO117" s="9"/>
@@ -14411,11 +14738,11 @@
         <v>29.4</v>
       </c>
       <c r="L118" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8.9999999999999858E-2</v>
       </c>
       <c r="M118" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>29.49</v>
       </c>
       <c r="N118" s="9"/>
@@ -14429,21 +14756,21 @@
         <v>0</v>
       </c>
       <c r="T118" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.8979999999999997</v>
       </c>
       <c r="U118" s="4"/>
       <c r="V118" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W118" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W118" s="9"/>
       <c r="X118" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30.539674465920651</v>
       </c>
       <c r="Y118" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>30.539674465920651</v>
       </c>
       <c r="Z118" s="9">
@@ -14478,10 +14805,13 @@
       </c>
       <c r="AJ118" s="9"/>
       <c r="AK118" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL118" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL118" s="9">
+        <f t="shared" si="24"/>
+        <v>13.904527272727272</v>
+      </c>
       <c r="AM118" s="9"/>
       <c r="AN118" s="9"/>
       <c r="AO118" s="9"/>
@@ -14526,11 +14856,11 @@
         <v>71.5</v>
       </c>
       <c r="L119" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2.284000000000006</v>
       </c>
       <c r="M119" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>69.215999999999994</v>
       </c>
       <c r="N119" s="9"/>
@@ -14544,21 +14874,21 @@
         <v>0</v>
       </c>
       <c r="T119" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.8432</v>
       </c>
       <c r="U119" s="4"/>
       <c r="V119" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W119" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W119" s="9"/>
       <c r="X119" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20.259260864539989</v>
       </c>
       <c r="Y119" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>20.259260864539989</v>
       </c>
       <c r="Z119" s="9">
@@ -14595,10 +14925,13 @@
         <v>58</v>
       </c>
       <c r="AK119" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL119" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL119" s="9">
+        <f t="shared" si="24"/>
+        <v>27.827672727272727</v>
+      </c>
       <c r="AM119" s="9"/>
       <c r="AN119" s="9"/>
       <c r="AO119" s="9"/>
@@ -14643,11 +14976,11 @@
         <v>24.6</v>
       </c>
       <c r="L120" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-7.6159999999999997</v>
       </c>
       <c r="M120" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>16.984000000000002</v>
       </c>
       <c r="N120" s="9"/>
@@ -14661,21 +14994,21 @@
         <v>0</v>
       </c>
       <c r="T120" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.3968000000000003</v>
       </c>
       <c r="U120" s="4"/>
       <c r="V120" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W120" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W120" s="9"/>
       <c r="X120" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20.062764955252003</v>
       </c>
       <c r="Y120" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>20.062764955252003</v>
       </c>
       <c r="Z120" s="9">
@@ -14712,10 +15045,13 @@
         <v>58</v>
       </c>
       <c r="AK120" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL120" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL120" s="9">
+        <f t="shared" si="24"/>
+        <v>5.4833818181818179</v>
+      </c>
       <c r="AM120" s="9"/>
       <c r="AN120" s="9"/>
       <c r="AO120" s="9"/>
@@ -14760,11 +15096,11 @@
         <v>824.5</v>
       </c>
       <c r="L121" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-14.850000000000023</v>
       </c>
       <c r="M121" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>809.65</v>
       </c>
       <c r="N121" s="9"/>
@@ -14780,21 +15116,21 @@
         <v>0</v>
       </c>
       <c r="T121" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>161.93</v>
       </c>
       <c r="U121" s="4"/>
       <c r="V121" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W121" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W121" s="9"/>
       <c r="X121" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.737250663867103</v>
       </c>
       <c r="Y121" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.737250663867103</v>
       </c>
       <c r="Z121" s="9">
@@ -14829,10 +15165,13 @@
       </c>
       <c r="AJ121" s="9"/>
       <c r="AK121" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL121" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL121" s="9">
+        <f t="shared" si="24"/>
+        <v>160.35989090909092</v>
+      </c>
       <c r="AM121" s="9"/>
       <c r="AN121" s="9"/>
       <c r="AO121" s="9"/>
@@ -14873,11 +15212,11 @@
         <v>163</v>
       </c>
       <c r="L122" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
       <c r="M122" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>169</v>
       </c>
       <c r="N122" s="9"/>
@@ -14891,23 +15230,23 @@
         <v>0</v>
       </c>
       <c r="T122" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>33.799999999999997</v>
       </c>
       <c r="U122" s="4">
         <v>500</v>
       </c>
       <c r="V122" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>500</v>
       </c>
-      <c r="W122" s="19"/>
+      <c r="W122" s="9"/>
       <c r="X122" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.828402366863907</v>
       </c>
       <c r="Y122" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.0355029585798818</v>
       </c>
       <c r="Z122" s="9">
@@ -14944,10 +15283,13 @@
         <v>177</v>
       </c>
       <c r="AK122" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>125</v>
       </c>
-      <c r="AL122" s="9"/>
+      <c r="AL122" s="9">
+        <f t="shared" si="24"/>
+        <v>3.0772727272727267</v>
+      </c>
       <c r="AM122" s="9"/>
       <c r="AN122" s="9"/>
       <c r="AO122" s="9"/>
@@ -14990,11 +15332,11 @@
         <v>77</v>
       </c>
       <c r="L123" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2</v>
       </c>
       <c r="M123" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79</v>
       </c>
       <c r="N123" s="9"/>
@@ -15008,23 +15350,23 @@
         <v>0</v>
       </c>
       <c r="T123" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>15.8</v>
       </c>
       <c r="U123" s="4">
         <v>500</v>
       </c>
       <c r="V123" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>500</v>
       </c>
-      <c r="W123" s="19"/>
+      <c r="W123" s="9"/>
       <c r="X123" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>39.556962025316452</v>
       </c>
       <c r="Y123" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.9113924050632907</v>
       </c>
       <c r="Z123" s="9">
@@ -15061,10 +15403,13 @@
         <v>177</v>
       </c>
       <c r="AK123" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>163</v>
       </c>
-      <c r="AL123" s="9"/>
+      <c r="AL123" s="9">
+        <f t="shared" si="24"/>
+        <v>1.4422727272727274</v>
+      </c>
       <c r="AM123" s="9"/>
       <c r="AN123" s="9"/>
       <c r="AO123" s="9"/>
@@ -15105,11 +15450,11 @@
         <v>166</v>
       </c>
       <c r="L124" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
       <c r="M124" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>172</v>
       </c>
       <c r="N124" s="9"/>
@@ -15123,23 +15468,23 @@
         <v>0</v>
       </c>
       <c r="T124" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>34.4</v>
       </c>
       <c r="U124" s="4">
         <v>500</v>
       </c>
       <c r="V124" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>500</v>
       </c>
-      <c r="W124" s="19"/>
+      <c r="W124" s="9"/>
       <c r="X124" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.465116279069768</v>
       </c>
       <c r="Y124" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.93023255813953487</v>
       </c>
       <c r="Z124" s="9">
@@ -15176,10 +15521,13 @@
         <v>177</v>
       </c>
       <c r="AK124" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>125</v>
       </c>
-      <c r="AL124" s="9"/>
+      <c r="AL124" s="9">
+        <f t="shared" si="24"/>
+        <v>3.1318181818181814</v>
+      </c>
       <c r="AM124" s="9"/>
       <c r="AN124" s="9"/>
       <c r="AO124" s="9"/>
@@ -15224,11 +15572,11 @@
         <v>168</v>
       </c>
       <c r="L125" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-8</v>
       </c>
       <c r="M125" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>160</v>
       </c>
       <c r="N125" s="9"/>
@@ -15244,21 +15592,21 @@
         <v>0</v>
       </c>
       <c r="T125" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>32</v>
       </c>
       <c r="U125" s="4"/>
       <c r="V125" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W125" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W125" s="9"/>
       <c r="X125" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12.6225</v>
       </c>
       <c r="Y125" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>12.6225</v>
       </c>
       <c r="Z125" s="9">
@@ -15293,10 +15641,13 @@
       </c>
       <c r="AJ125" s="9"/>
       <c r="AK125" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL125" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL125" s="9">
+        <f t="shared" si="24"/>
+        <v>34.909090909090907</v>
+      </c>
       <c r="AM125" s="9"/>
       <c r="AN125" s="9"/>
       <c r="AO125" s="9"/>
@@ -15341,11 +15692,11 @@
         <v>136</v>
       </c>
       <c r="L126" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-13</v>
       </c>
       <c r="M126" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>123</v>
       </c>
       <c r="N126" s="9"/>
@@ -15359,24 +15710,24 @@
         <v>0</v>
       </c>
       <c r="T126" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>24.6</v>
       </c>
       <c r="U126" s="4">
-        <f t="shared" ref="U126" si="31">11*T126-S126-R126-Q126-P126-O126-F126</f>
+        <f t="shared" ref="U126" si="33">11*T126-S126-R126-Q126-P126-O126-F126</f>
         <v>3.6000000000000227</v>
       </c>
       <c r="V126" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.6000000000000227</v>
       </c>
-      <c r="W126" s="19"/>
+      <c r="W126" s="9"/>
       <c r="X126" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11</v>
       </c>
       <c r="Y126" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10.853658536585366</v>
       </c>
       <c r="Z126" s="9">
@@ -15411,10 +15762,13 @@
       </c>
       <c r="AJ126" s="9"/>
       <c r="AK126" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="AL126" s="9"/>
+      <c r="AL126" s="9">
+        <f t="shared" si="24"/>
+        <v>22.745454545454546</v>
+      </c>
       <c r="AM126" s="9"/>
       <c r="AN126" s="9"/>
       <c r="AO126" s="9"/>
@@ -15459,11 +15813,11 @@
         <v>14.7</v>
       </c>
       <c r="L127" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1.2929999999999993</v>
       </c>
       <c r="M127" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.407</v>
       </c>
       <c r="N127" s="9"/>
@@ -15477,21 +15831,21 @@
         <v>0</v>
       </c>
       <c r="T127" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.6814</v>
       </c>
       <c r="U127" s="4"/>
       <c r="V127" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W127" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W127" s="9"/>
       <c r="X127" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.781308271798315</v>
       </c>
       <c r="Y127" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15.781308271798315</v>
       </c>
       <c r="Z127" s="9">
@@ -15526,10 +15880,13 @@
       </c>
       <c r="AJ127" s="9"/>
       <c r="AK127" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL127" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL127" s="9">
+        <f t="shared" si="24"/>
+        <v>2.7199454545454547</v>
+      </c>
       <c r="AM127" s="9"/>
       <c r="AN127" s="9"/>
       <c r="AO127" s="9"/>
@@ -15574,11 +15931,11 @@
         <v>108</v>
       </c>
       <c r="L128" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-9</v>
       </c>
       <c r="M128" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>99</v>
       </c>
       <c r="N128" s="9"/>
@@ -15592,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="T128" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>19.8</v>
       </c>
       <c r="U128" s="4">
@@ -15600,16 +15957,16 @@
         <v>35.400000000000006</v>
       </c>
       <c r="V128" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>35.400000000000006</v>
       </c>
-      <c r="W128" s="19"/>
+      <c r="W128" s="9"/>
       <c r="X128" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
       <c r="Y128" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>6.2121212121212119</v>
       </c>
       <c r="Z128" s="9">
@@ -15644,10 +16001,13 @@
       </c>
       <c r="AJ128" s="9"/>
       <c r="AK128" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
-      <c r="AL128" s="9"/>
+      <c r="AL128" s="9">
+        <f t="shared" si="24"/>
+        <v>18.163636363636364</v>
+      </c>
       <c r="AM128" s="9"/>
       <c r="AN128" s="9"/>
       <c r="AO128" s="9"/>
@@ -15692,11 +16052,11 @@
         <v>27</v>
       </c>
       <c r="L129" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M129" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>27</v>
       </c>
       <c r="N129" s="9"/>
@@ -15710,21 +16070,21 @@
         <v>0</v>
       </c>
       <c r="T129" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.4</v>
       </c>
       <c r="U129" s="4"/>
       <c r="V129" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W129" s="19"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W129" s="9"/>
       <c r="X129" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20.999999999999996</v>
       </c>
       <c r="Y129" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>20.999999999999996</v>
       </c>
       <c r="Z129" s="9">
@@ -15761,10 +16121,13 @@
         <v>58</v>
       </c>
       <c r="AK129" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL129" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL129" s="9">
+        <f t="shared" si="24"/>
+        <v>8.290909090909091</v>
+      </c>
       <c r="AM129" s="9"/>
       <c r="AN129" s="9"/>
       <c r="AO129" s="9"/>
@@ -15805,11 +16168,11 @@
         <v>5</v>
       </c>
       <c r="L130" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M130" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>5</v>
       </c>
       <c r="N130" s="11"/>
@@ -15819,21 +16182,21 @@
       <c r="R130" s="11"/>
       <c r="S130" s="11"/>
       <c r="T130" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="U130" s="13"/>
       <c r="V130" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W130" s="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W130" s="11"/>
       <c r="X130" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="Y130" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-5</v>
       </c>
       <c r="Z130" s="11">
@@ -15868,10 +16231,13 @@
       </c>
       <c r="AJ130" s="11"/>
       <c r="AK130" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL130" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL130" s="9">
+        <f t="shared" si="24"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
       <c r="AM130" s="9"/>
       <c r="AN130" s="9"/>
       <c r="AO130" s="9"/>
@@ -15910,11 +16276,11 @@
       </c>
       <c r="K131" s="11"/>
       <c r="L131" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M131" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N131" s="11"/>
@@ -15926,21 +16292,21 @@
         <v>0</v>
       </c>
       <c r="T131" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U131" s="13"/>
       <c r="V131" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="W131" s="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W131" s="11"/>
       <c r="X131" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y131" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z131" s="11">
@@ -15975,10 +16341,13 @@
       </c>
       <c r="AJ131" s="11"/>
       <c r="AK131" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL131" s="9"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL131" s="9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AM131" s="9"/>
       <c r="AN131" s="9"/>
       <c r="AO131" s="9"/>
